--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일일정치주요뉴스" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="일일정치주요뉴스" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,16 +39,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="000563C1"/>
-      <sz val="10"/>
-      <u val="single"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -76,16 +66,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -451,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -482,12 +468,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>與, 이달 중 메가특구특별법 발의</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/016/0000000001</t>
+          <t>(해당 시간대 기사 없음)</t>
         </is>
       </c>
     </row>
@@ -499,7 +480,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>(해당 시간대 기사 없음)</t>
         </is>
@@ -513,7 +494,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>(해당 시간대 기사 없음)</t>
         </is>
@@ -527,7 +508,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>(해당 시간대 기사 없음)</t>
         </is>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +39,16 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -66,12 +76,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -468,47 +482,112 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>(해당 시간대 기사 없음)</t>
+          <t>7월8일 모닝뉴스 헤드라인</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.radiokorea.com/news/article.php?uid=498847</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>조경태 "국힘 50%가 친윤…내란 옹호 세력 물갈이해야</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/018/0006325649?sid=100</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2) 더불어민주당 동정</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>[홍태화의 USA 인사이트] 앞으로 4년은 차기 대통령의 ‘외교 예습’ 기...</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/023/0003986521?sid=103</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>원 구성 공회전에도 민주당은 간다…'단독 국회' 본격 가동</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/119/0003109485?sid=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>"재검표" 이구동성 외쳤지만...절차 두곤 '동상이몽'</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/052/0002376726?sid=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>[미리보는 이데일리 신문] 부모님 찬스 없으면 서울 전세도 못산다</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/018/0006325644?sid=101</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2) 더불어민주당 동정</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
           <t>(해당 시간대 기사 없음)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>3) 국민의힘 동정</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>(해당 시간대 기사 없음)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>4) 경제 동정</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>(해당 시간대 기사 없음)</t>
         </is>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>(기준: 2026-07-08 22:00 ~ 2026-07-09 08:00)</t>
+          <t>(기준: 2026-07-08 22:00 ~ 2026-07-09 06:00)</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -476,72 +476,72 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[인터뷰] 황현선 "민주당, 합당 원하면 사과부터…아니면 약탈 정치"</t>
+          <t>윤석열 ‘유죄’ 나온 명태균 여론조사…김건희·오세훈에도 영향 미칠...</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009059819?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/032/0003458190?sid=102</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>"11년 묶인 담뱃값, 사실상 내린 셈…일회성 아닌 지속 인상"</t>
+          <t>“집회 오라” 전화 거는 장동혁 측근들, 전화 피하는 의원들</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009059818?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003537661?sid=100</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>당신의 ‘생각’은 안녕하신가요[신간]</t>
+          <t>장동혁·정점식, 모처럼 '보완수사권' 한뜻… 한동훈까지 단일대오 움직...</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/033/0000051342?sid=103</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942308?sid=100</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[사설] 생활 밀착 공약, 이제는 '실행력'으로 답해야</t>
+          <t>송영길 "정청래, 대선 출마 안 한다? 누가 출마하랬나"</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://www.cctoday.co.kr/news/articleView.html?idxno=2233268</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002448429?sid=100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[허정수칼럼] 호남 반도체 논란, 삼성·SK가 답할 차례</t>
+          <t>김민석 "지난 1년간 당정관계 잘 안 돼, 당대표 자기 정치 때문"</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/293/0000087639?sid=110</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002448428?sid=100</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[기자의눈] 제2의 장윤기 사건이 나오지 않으려면</t>
+          <t>오세훈 “서울 주택 행정은…” 李대통령 “그 얘기는 나중에 하시죠”</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260714031707434</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003987663?sid=100</t>
         </is>
       </c>
     </row>
@@ -555,36 +555,36 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>대전 원도심 공약 '경제 회복' 초점 [지방의원 공약추적단 시즌2]</t>
+          <t>‘조국당과 합당 무산’ 김민석에 화살 돌리는 정청래</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>https://www.cctoday.co.kr/news/articleView.html?idxno=2233262</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003733978?sid=100</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>‘서울대와 협업(UP)’ 관악S밸리 고도화…“벤처창업도시로 질적 도약...</t>
+          <t>정청래 “보완수사권 존치론 당황”…당 정체성·검찰개혁 강조</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2603527</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006330307?sid=100</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>코인 현물 ETF 밑그림 나왔다…"김프 없애고 선물시장 도입"</t>
+          <t>정청래, '보완수사권 일부 존치' 제기에 "정말 손 많이 가는 당"</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/001/0016194810?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009059665?sid=100</t>
         </is>
       </c>
     </row>
@@ -598,36 +598,36 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>[오늘의 주요일정]사회(7월15일 수요일)</t>
+          <t>[단독] 장동혁, 경기도당 위원장으로 '최측근' 조광한 띄우기, 당권파 세...</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014067086?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942299?sid=100</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>[헐크 이만수의 힘] 아시아 야구의 새로운 지평, 이윤 대표와 함께 걷는...</t>
+          <t>장동혁, '재선거' 고리로 전국 돌며 지지층 확보 총력…오늘 광주행</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>https://www.nbntv.co.kr/news/articleView.html?idxno=4023002</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014067055?sid=100</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>반도체만 잘 나갔다…고용절벽에 꺼낸 '20만 AI 인재' 카드</t>
+          <t>오세훈 “부동산 한말씀 드려도 되겠나” 한성숙 “서류로 받겠다”</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005386139?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003733968?sid=100</t>
         </is>
       </c>
     </row>
@@ -641,36 +641,36 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>“무역장벽 제거되면 對中 화장품 수출 27% ↑”</t>
+          <t>[단독]4년 만에 도로 ‘컬러풀 대구’?···도시브랜드 교체에 또 수억...</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://www.yakup.com/news/index.html?mode=view&amp;cat=12&amp;nid=329780</t>
+          <t>https://n.news.naver.com/mnews/article/032/0003458192?sid=102</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>빚에 쫓기는 위기가구 찾는다…불법사금융 피해 정보 연계</t>
+          <t>수출 4강 '가시권'·소득 5만불 '환율 변수'…잠재성장 3%는 '험로'</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014067095?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009059814?sid=101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>[단독]4년 만에 도로 ‘컬러풀 대구’?···도시브랜드 교체에 또 수억...</t>
+          <t>"교사·학생도 경제·금융 알아야"…서울교육청, 연수·수업 연계</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/032/0003458192?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014067116?sid=102</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -476,7 +476,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>윤석열 ‘유죄’ 나온 명태균 여론조사…김건희·오세훈에도 영향 미칠...</t>
+          <t>[경향신문] 윤석열 ‘유죄’ 나온 명태균 여론조사…김건희·오세훈에도 영향 미칠...</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -488,7 +488,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>“집회 오라” 전화 거는 장동혁 측근들, 전화 피하는 의원들</t>
+          <t>[중앙일보] “집회 오라” 전화 거는 장동혁 측근들, 전화 피하는 의원들</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -500,7 +500,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>장동혁·정점식, 모처럼 '보완수사권' 한뜻… 한동훈까지 단일대오 움직...</t>
+          <t>[한국일보] 장동혁·정점식, 모처럼 '보완수사권' 한뜻… 한동훈까지 단일대오 움직...</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -512,36 +512,36 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>송영길 "정청래, 대선 출마 안 한다? 누가 출마하랬나"</t>
+          <t>[조선일보] 버티던 정청래, 선호투표 수용… 친명 “동정표 노리고 선회”</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002448429?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003987664?sid=100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>김민석 "지난 1년간 당정관계 잘 안 돼, 당대표 자기 정치 때문"</t>
+          <t>[조선일보] 오세훈 “서울 주택 행정은…” 李대통령 “그 얘기는 나중에 하시죠”</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002448428?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003987663?sid=100</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>오세훈 “서울 주택 행정은…” 李대통령 “그 얘기는 나중에 하시죠”</t>
+          <t>[문화일보] 박범계 “정청래, 누구보다 사나워…스스로 약자 표현 적절치 않아”</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003987663?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/021/0002804698?sid=100</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>‘조국당과 합당 무산’ 김민석에 화살 돌리는 정청래</t>
+          <t>[동아일보] ‘조국당과 합당 무산’ 김민석에 화살 돌리는 정청래</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>정청래 “보완수사권 존치론 당황”…당 정체성·검찰개혁 강조</t>
+          <t>[이데일리] 정청래 “보완수사권 존치론 당황”…당 정체성·검찰개혁 강조</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>정청래, '보완수사권 일부 존치' 제기에 "정말 손 많이 가는 당"</t>
+          <t>[뉴스1] 정청래, '보완수사권 일부 존치' 제기에 "정말 손 많이 가는 당"</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -598,7 +598,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>[단독] 장동혁, 경기도당 위원장으로 '최측근' 조광한 띄우기, 당권파 세...</t>
+          <t>[한국일보] [단독] 장동혁, 경기도당 위원장으로 '최측근' 조광한 띄우기, 당권파 세...</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -610,7 +610,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>장동혁, '재선거' 고리로 전국 돌며 지지층 확보 총력…오늘 광주행</t>
+          <t>[뉴시스] 장동혁, '재선거' 고리로 전국 돌며 지지층 확보 총력…오늘 광주행</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -622,7 +622,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>오세훈 “부동산 한말씀 드려도 되겠나” 한성숙 “서류로 받겠다”</t>
+          <t>[동아일보] 오세훈 “부동산 한말씀 드려도 되겠나” 한성숙 “서류로 받겠다”</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -641,7 +641,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>[단독]4년 만에 도로 ‘컬러풀 대구’?···도시브랜드 교체에 또 수억...</t>
+          <t>[경향신문] [단독]4년 만에 도로 ‘컬러풀 대구’?···도시브랜드 교체에 또 수억...</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -653,24 +653,24 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>수출 4강 '가시권'·소득 5만불 '환율 변수'…잠재성장 3%는 '험로'</t>
+          <t>[경향신문] ‘한국 가면 여행가방 가득 화장품’···내수 소비 끌어올린 건 알고...</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009059814?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/032/0003458196?sid=101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>"교사·학생도 경제·금융 알아야"…서울교육청, 연수·수업 연계</t>
+          <t>[머니투데이] 계좌 파랗게 질려도 '월 500만원' 따박따박…폭락장 버틴 50대의 비결</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014067116?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005386148?sid=101</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -512,24 +512,24 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[조선일보] 버티던 정청래, 선호투표 수용… 친명 “동정표 노리고 선회”</t>
+          <t>[조선일보] 오세훈 “서울 주택 행정은…” 李대통령 “그 얘기는 나중에 하시죠”</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003987664?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003987663?sid=100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[조선일보] 오세훈 “서울 주택 행정은…” 李대통령 “그 얘기는 나중에 하시죠”</t>
+          <t>[조선일보] 버티던 정청래, 선호투표 수용… 친명 “동정표 노리고 선회”</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003987663?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003987664?sid=100</t>
         </is>
       </c>
     </row>
@@ -653,24 +653,24 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>[경향신문] ‘한국 가면 여행가방 가득 화장품’···내수 소비 끌어올린 건 알고...</t>
+          <t>[뉴시스] "교사·학생도 경제·금융 알아야"…서울교육청, 연수·수업 연계</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/032/0003458196?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014067116?sid=102</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] 계좌 파랗게 질려도 '월 500만원' 따박따박…폭락장 버틴 50대의 비결</t>
+          <t>[뉴스1] 수출 4강 '가시권'·소득 5만불 '환율 변수'…잠재성장 3%는 '험로'</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005386148?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009059814?sid=101</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +49,11 @@
       <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00999999"/>
     </font>
   </fonts>
   <fills count="2">
@@ -71,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -80,6 +85,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -476,72 +482,72 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[경향신문] 윤석열 ‘유죄’ 나온 명태균 여론조사…김건희·오세훈에도 영향 미칠...</t>
+          <t>[서울신문] 민주 “즉각 재검표”… 국힘 “특검 먼저” “병행” 갈려</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/032/0003458190?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/081/0003661217?sid=100</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] “집회 오라” 전화 거는 장동혁 측근들, 전화 피하는 의원들</t>
+          <t>[중앙일보] “盧 퇴임후 재수사 없게 해달라” 靑민정실 요구, 檢은 거부했다</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003537661?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003537658?sid=102</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[한국일보] 장동혁·정점식, 모처럼 '보완수사권' 한뜻… 한동훈까지 단일대오 움직...</t>
+          <t>[동아일보] 與 “투표지 247만장 즉각 재검표” 野 “특검 우선”</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942308?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003734017?sid=102</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[조선일보] 오세훈 “서울 주택 행정은…” 李대통령 “그 얘기는 나중에 하시죠”</t>
+          <t>[조선일보] 국힘 소속 특위 위원장 “재검표를”… 국힘 특위 위원들은 “특검이 먼...</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003987663?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003987666?sid=100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[조선일보] 버티던 정청래, 선호투표 수용… 친명 “동정표 노리고 선회”</t>
+          <t>[뉴스1] 與 "즉각 재검표"…野는 "특검과 병행"·"특검 먼저" 두 갈래(종합2보)</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003987664?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009059721?sid=100</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[문화일보] 박범계 “정청래, 누구보다 사나워…스스로 약자 표현 적절치 않아”</t>
+          <t>[연합뉴스] 선관위 국조 '재검표' 합의 불발…與 "즉각"·국힘 "특검 우선"(종합)</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002804698?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/001/0016194717?sid=100</t>
         </is>
       </c>
     </row>
@@ -553,124 +559,37 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>[동아일보] ‘조국당과 합당 무산’ 김민석에 화살 돌리는 정청래</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003733978?sid=100</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>[이데일리] 정청래 “보완수사권 존치론 당황”…당 정체성·검찰개혁 강조</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006330307?sid=100</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>(해당 시간대 기사 없음)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>[뉴스1] 정청래, '보완수사권 일부 존치' 제기에 "정말 손 많이 가는 당"</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009059665?sid=100</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>3) 국민의힘 동정</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>(해당 시간대 기사 없음)</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>[한국일보] [단독] 장동혁, 경기도당 위원장으로 '최측근' 조광한 띄우기, 당권파 세...</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942299?sid=100</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>4) 경제 동정</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>[뉴시스] 장동혁, '재선거' 고리로 전국 돌며 지지층 확보 총력…오늘 광주행</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014067055?sid=100</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>[동아일보] 오세훈 “부동산 한말씀 드려도 되겠나” 한성숙 “서류로 받겠다”</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003733968?sid=100</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>4) 경제 동정</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>[경향신문] [단독]4년 만에 도로 ‘컬러풀 대구’?···도시브랜드 교체에 또 수억...</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/032/0003458192?sid=102</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>[뉴시스] "교사·학생도 경제·금융 알아야"…서울교육청, 연수·수업 연계</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014067116?sid=102</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>[뉴스1] 수출 4강 '가시권'·소득 5만불 '환율 변수'…잠재성장 3%는 '험로'</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009059814?sid=101</t>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>(해당 시간대 기사 없음)</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -551,43 +551,67 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>[연합뉴스] 與 "투표포기 인원도 파악못해"…국힘 "선피아 카르텔 드러나"(종합2보...</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/001/0016194712?sid=100</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[데일리안] 여야, 선관위 한목소리 질타…"투표 관리부터 전관 특혜까지 총체적 부...</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/119/0003111468?sid=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>2) 더불어민주당 동정</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>(해당 시간대 기사 없음)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>3) 국민의힘 동정</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>(해당 시간대 기사 없음)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>4) 경제 동정</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>(해당 시간대 기사 없음)</t>
         </is>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,11 +50,6 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00999999"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -76,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -85,7 +80,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -451,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -461,14 +455,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>일일 정치 주요뉴스 7/15(수)</t>
+          <t>일일 정치 주요뉴스 7/16(목)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>(기준: 2026-07-14 22:00 ~ 2026-07-15 06:00)</t>
+          <t>(기준: 2026-07-15 22:00 ~ 2026-07-16 06:00)</t>
         </is>
       </c>
     </row>
@@ -482,96 +476,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 민주 “즉각 재검표”… 국힘 “특검 먼저” “병행” 갈려</t>
+          <t>[뉴스1] "국무회의부터 당내 회동까지"…오세훈, 민선9기 광폭 행보</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/081/0003661217?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009062205?sid=102</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] “盧 퇴임후 재수사 없게 해달라” 靑민정실 요구, 檢은 거부했다</t>
+          <t>[노컷뉴스] 정청래·김민석, 오송 3주기 추모 '따로'…등록 하루 앞 충청 당심 공략</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003537658?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/079/0004168932?sid=100</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 與 “투표지 247만장 즉각 재검표” 野 “특검 우선”</t>
+          <t>[서울신문] 유시민 “李, 실패로 끝날 것”… 송영길은 ‘鄭 공천 후회’ 낙태 비유</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003734017?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/081/0003661600?sid=100</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[조선일보] 국힘 소속 특위 위원장 “재검표를”… 국힘 특위 위원들은 “특검이 먼...</t>
+          <t>[중앙일보] 오세훈과 밥 먹고, 한동훈과 모임…국힘 아슬아슬 ‘눈치작전’</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003987666?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003537936?sid=100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] 與 "즉각 재검표"…野는 "특검과 병행"·"특검 먼저" 두 갈래(종합2보)</t>
+          <t>[동아일보] 장동혁 홀로 외치는 “전면 재선거”… 국힘 대변인 논평 346건에선 ‘0...</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009059721?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003734325?sid=100</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스] 선관위 국조 '재검표' 합의 불발…與 "즉각"·국힘 "특검 우선"(종합)</t>
+          <t>[동아일보] 송영길 “먼저 의원된 정청래, 대통령 깔봐” 2007년 명청관계까지 ‘파...</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/001/0016194717?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003734324?sid=100</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스] 與 "투표포기 인원도 파악못해"…국힘 "선피아 카르텔 드러나"(종합2보...</t>
+          <t>[한국일보] 김민석 "민주 대통합", 정청래 "강력한 개혁" … 與 '3인 3색' 노선 경쟁</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/001/0016194712?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942539?sid=100</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[데일리안] 여야, 선관위 한목소리 질타…"투표 관리부터 전관 특혜까지 총체적 부...</t>
+          <t>[조선일보] 송영길 “채상병 사건 연루자 추가 고발”</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003111468?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003987908?sid=100</t>
         </is>
       </c>
     </row>
@@ -583,37 +577,196 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>(해당 시간대 기사 없음)</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>[중앙일보] “의원들이 날 안 좋아해” 또 나왔다, 정청래 1년 전 전략 소환</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/025/0003537944?sid=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>[경향신문] 유시민 ‘이재명 대통령 필연적 실패’ 발언에 민주당 “저주와 다르지...</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/032/0003458454?sid=100</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>[조선일보] 정청래, 오송 참사 3주기 헌화</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/023/0003987904?sid=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>[경향신문] “신고할 테면 해봐”…직장내괴롭힘금지법 7년, ‘5인 미만’이란 갑질...</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/032/0003458459?sid=102</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>[SBS] "한라산 백록담 들어가 물 떠먹기도…불법 탐방 근절해야"</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/055/0001372896?sid=102</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>3) 국민의힘 동정</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>(해당 시간대 기사 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>[KBS] 국힘 장동혁 대표 광주서 ‘재선거 촉구’ 집회 참석</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/056/0012219067?sid=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>[노컷뉴스] [단독]수사감찰 대상 경찰 급증…장윤기 전에도 '증거인멸' 4건</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/079/0004168929?sid=102</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>[뉴스1] '文 정부 블랙리스트' 조명균 전 통일장관 오늘 대법 선고</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/421/0009062214?sid=102</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>[서울신문] 대출 금리 0.25% 포인트 오르면 가계 이자 연 3조3000억 ‘눈덩이’</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/081/0003661647?sid=101</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>[한겨레] “다 해놓은 수사 뺏길라”…경찰, 중수청 ‘사건 이첩요구권’ 견제 본...</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/028/0002814321?sid=102</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>4) 경제 동정</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>(해당 시간대 기사 없음)</t>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>[더팩트] 오세훈표 '야간경제' 시동…관광·상권 살리기 시험대</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/629/0000516524?sid=102</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>[동아일보] [단독]“신입 대신 AI 쓴다” 韓주요 IT기업 20대 신규채용 43% 감소</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/020/0003734311?sid=102</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>[경향신문] ‘청년 일자리’에 재정 쏟았지만 ‘6개월 인턴’으론 안돼…“기업이...</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/032/0003458458?sid=101</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>[뉴시스] '사필귀정' 황우석 최고과학기술인상 박탈…학계 "22년 걸릴 일인가"</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/003/0014069771?sid=105</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>[연합뉴스TV] [현생탐구] "이 촉감 못 참죠"…'손맛' 찾아 동대문 말랑이 거리로</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/422/0000885583?sid=101</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -455,14 +455,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>일일 정치 주요뉴스 7/16(목)</t>
+          <t>일일 정치 주요뉴스 7/17(금)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>(기준: 2026-07-15 22:00 ~ 2026-07-16 06:00)</t>
+          <t>(기준: 2026-07-16 22:00 ~ 2026-07-17 06:00)</t>
         </is>
       </c>
     </row>
@@ -476,96 +476,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] "국무회의부터 당내 회동까지"…오세훈, 민선9기 광폭 행보</t>
+          <t>[노컷뉴스] 송영길·김용 전대 출마 자격 '빨간불'…17일 재논의</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009062205?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/079/0004169350?sid=100</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[노컷뉴스] 정청래·김민석, 오송 3주기 추모 '따로'…등록 하루 앞 충청 당심 공략</t>
+          <t>[한국일보] 여전히 "재선거"만 외치는 장동혁... 당내서도 등 돌렸다</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004168932?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942767?sid=100</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 유시민 “李, 실패로 끝날 것”… 송영길은 ‘鄭 공천 후회’ 낙태 비유</t>
+          <t>[동아일보] 강성층 결집 밀착하는 정청래-유시민… 친명 “대통령을 적으로 만들어...</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/081/0003661600?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003734554?sid=100</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] 오세훈과 밥 먹고, 한동훈과 모임…국힘 아슬아슬 ‘눈치작전’</t>
+          <t>[뉴스1] '후보 자격 논란' 송영길·김용 "검찰 탄압, 예외 사유"…與, 17일 재논의</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003537936?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009064683?sid=100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 장동혁 홀로 외치는 “전면 재선거”… 국힘 대변인 논평 346건에선 ‘0...</t>
+          <t>[연합뉴스] 與최고위, '친명' 송영길·김용 후보 자격 격론…친청계 반대(종합)</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003734325?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/001/0016200022?sid=100</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 송영길 “먼저 의원된 정청래, 대통령 깔봐” 2007년 명청관계까지 ‘파...</t>
+          <t>[문화일보] “張, 내게 싸움 걸어 어떻게든 연명…대꾸할 필요 못 느껴” 한동훈의...</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003734324?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/021/0002805251?sid=100</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[한국일보] 김민석 "민주 대통합", 정청래 "강력한 개혁" … 與 '3인 3색' 노선 경쟁</t>
+          <t>[뉴스1] 與 심야 최고위 '송영길·김용 출마 자격' 심사…17일에 재논의(종합)</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942539?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009064680?sid=100</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[조선일보] 송영길 “채상병 사건 연루자 추가 고발”</t>
+          <t>[한겨레] ‘복당 6개월 미만’ 송영길 전대 출마 불가?…민주 심야 최고위 결론 ...</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003987908?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/028/0002814521?sid=100</t>
         </is>
       </c>
     </row>
@@ -579,60 +579,60 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] “의원들이 날 안 좋아해” 또 나왔다, 정청래 1년 전 전략 소환</t>
+          <t>[YTN] 송영길 "유시민 충정 이해하나 악담은 맞지 않아"</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003537944?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/052/0002380692?sid=100</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>[경향신문] 유시민 ‘이재명 대통령 필연적 실패’ 발언에 민주당 “저주와 다르지...</t>
+          <t>[뉴시스] 김민석 "송영길·김용 후보등록 허용해야…충분한 예외 사유"</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/032/0003458454?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014072366?sid=100</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>[조선일보] 정청래, 오송 참사 3주기 헌화</t>
+          <t>[뉴시스] '출마자격 도마' 송영길·김용 "檢탄압 피해자를 배제? 전대 정당성 의...</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003987904?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014072365?sid=100</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>[경향신문] “신고할 테면 해봐”…직장내괴롭힘금지법 7년, ‘5인 미만’이란 갑질...</t>
+          <t>[뉴시스] 강득구 "송영길에 '6개월 전 입당' 기준 지나치게 기계적…헌신 생각해...</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/032/0003458459?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014072363?sid=100</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>[SBS] "한라산 백록담 들어가 물 떠먹기도…불법 탐방 근절해야"</t>
+          <t>[중앙일보] ‘복당 6개월 미만’ 송영길, 출마 제동?…與, 심야 최고위원 소집</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/055/0001372896?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003538198?sid=100</t>
         </is>
       </c>
     </row>
@@ -646,60 +646,60 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>[KBS] 국힘 장동혁 대표 광주서 ‘재선거 촉구’ 집회 참석</t>
+          <t>[문화일보] [속보]보완수사권 ‘유지’ 55.4% ‘폐지’ 30.8%-리서치웰</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012219067?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/021/0002805248?sid=100</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>[노컷뉴스] [단독]수사감찰 대상 경찰 급증…장윤기 전에도 '증거인멸' 4건</t>
+          <t>[경향신문] “왜 고정형으로 안 했을까”···영끌·빚투족 비상, 금리 0.5%p 오르면...</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004168929?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/032/0003458735?sid=101</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] '文 정부 블랙리스트' 조명균 전 통일장관 오늘 대법 선고</t>
+          <t>[서울신문] ‘국민성장펀드 1호’ 신안우이 해상풍력 첫 삽… 국내 공급망 ‘바람’...</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009062214?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/081/0003662035?sid=101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 대출 금리 0.25% 포인트 오르면 가계 이자 연 3조3000억 ‘눈덩이’</t>
+          <t>[서울신문] “종부세, 주택 수 아닌 가액 부과” “양도세, 보유보다 거주 기간”…...</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/081/0003661647?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/081/0003661986?sid=101</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>[한겨레] “다 해놓은 수사 뺏길라”…경찰, 중수청 ‘사건 이첩요구권’ 견제 본...</t>
+          <t>[뉴스1] 백악관 "美, 이란 해상 재봉쇄에 미군 1만명·항모 2척 투입"</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/028/0002814321?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009064688?sid=104</t>
         </is>
       </c>
     </row>
@@ -713,60 +713,60 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>[더팩트] 오세훈표 '야간경제' 시동…관광·상권 살리기 시험대</t>
+          <t>[이데일리] [속보]AI 투자 회의론에 반도체주 '와르르'…나스닥 1.5% 급락</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000516524?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006332055?sid=101</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] [단독]“신입 대신 AI 쓴다” 韓주요 IT기업 20대 신규채용 43% 감소</t>
+          <t>[뉴스1] 5년 전 2%의 유혹…돌아온 '혼합형 금리 폭탄'[금리인상 후폭풍]①</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003734311?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009064724?sid=101</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>[경향신문] ‘청년 일자리’에 재정 쏟았지만 ‘6개월 인턴’으론 안돼…“기업이...</t>
+          <t>[경향신문] 손재주 없다던 남편 직업은 ‘외과의사’···가사노동 ‘머릿속 알람...</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/032/0003458458?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/032/0003458741?sid=103</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] '사필귀정' 황우석 최고과학기술인상 박탈…학계 "22년 걸릴 일인가"</t>
+          <t>[머니투데이] "챗GPT·클로드 크레딧 쏩니다"…AI 업체들 '공짜 토큰' 출혈 전쟁, 왜?</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014069771?sid=105</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005387286?sid=101</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스TV] [현생탐구] "이 촉감 못 참죠"…'손맛' 찾아 동대문 말랑이 거리로</t>
+          <t>[헤럴드경제] 금리·최저임금 인상에 중동 전쟁마저 격화…하반기 소상공인 덮칠 ‘다...</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/422/0000885583?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002671470?sid=101</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -455,14 +455,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>일일 정치 주요뉴스 7/18(토)</t>
+          <t>일일 정치 주요뉴스 7/19(일)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>(기준: 2026-07-17 22:00 ~ 2026-07-18 06:00)</t>
+          <t>(기준: 2026-07-18 22:00 ~ 2026-07-19 06:00)</t>
         </is>
       </c>
     </row>
@@ -476,96 +476,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] 길어지는 장동혁 거취 공방…국힘 내부 張 '장외 정치' 두고 우려도</t>
+          <t>[뉴시스] 與당권주자 메시지 경쟁 치열…김민석 '국정', 송영길 '실행', 정청래 '...</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014073196?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014073763?sid=100</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] 안철수·이준석 협공에 장동혁 '쐐기'…식어가는 한동훈 복당론</t>
+          <t>[연합뉴스] 임만균 서울시의장 "오세훈 시정 견제 강하게, 협력은 적극적으로"</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009065701?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/001/0016201448?sid=100</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 제헌절 경축식 불참 장동혁 “재선거” 장외정치</t>
+          <t>[세계일보] 오세훈 ‘여론조사비 대납’ 의혹 22일 선고…주요 쟁점은?</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003734733?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/022/0004144030?sid=102</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 與전대 송영길-김용 후보자격 시비 11시간만에 “예외적 허용” 봉합</t>
+          <t>[디지털타임스] 김민석 ‘적임론’·정청래 ‘동정론’·송영길 ‘정면돌파’… 첫 주말...</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003734730?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/029/0003037511?sid=100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] ‘자격미달’ 송영길 전대 출마 허용, 4년 전 박지현은 불허</t>
+          <t>[노컷뉴스] '尹체포방해' 나경원·김기현 부른 종합특검…성과 있을까</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/353/0000056087?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/079/0004169562?sid=102</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[조선일보] 오세훈 “정부, 청년 투전판 내몰고 빚 탕감 생색”</t>
+          <t>[디지털타임스] ‘친장동혁’ 조광한, 경기도당위원장 선거 출마 번복…“생각접어”</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003988261?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/029/0003037510?sid=100</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[더팩트] 오세훈 1심 선고 앞둔 서울시…"관심 갖지만 동요 없어"</t>
+          <t>[연합뉴스] "대안도 방법도 없다"…반장동혁, 張체제 사실상 방치 기류</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000516952?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/001/0016201432?sid=100</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[YTN] 송영길·김용 '예외 허용' 논란... 제헌절 경축식 '불참' 장동혁</t>
+          <t>[더팩트] [인터뷰] '비대위원장' 자처 조경태 "장동혁 대신 덧셈정치…한동훈 즉...</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/052/0002380943?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000517007?sid=100</t>
         </is>
       </c>
     </row>
@@ -579,194 +579,182 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] “하룻밤 만에 3억8000만원 쏟아졌다”…정청래 후원금 ‘폭발’</t>
+          <t>[경향신문] 정청래 “어머니 저는 어떡해야 하나요···만나는 사람마다 ‘괜찮냐...</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003538343?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/033/0000051388?sid=100</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] “檢 보완수사권 유지” 61%, “전면 폐지” 23%</t>
+          <t>[KBS] 대전 찾은 김민석 전 총리 “당 바로 잡을 시점”</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003734734?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012220627?sid=100</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>[조선일보] 검찰 보완수사권 61%가 “유지해야”</t>
+          <t>[더팩트] 채상병 순직 3주기…'첫 구속영장 기각' 특검 수사 고비</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003988272?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000517008?sid=102</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] 구청장 직속 재건축 팀 만들고 주택 정책 ‘1호 결재’…규제 완화는 과...</t>
+          <t>[YTN] 후보등록 마친 민주 당권주자들...본격 당심 행보</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/353/0000056083?sid=101</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>[KBS] 민주당 대표 후보들, 등록 마감 후 첫 주말…지역 당심 다잡기</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012220415?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/052/0002381274?sid=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>3) 국민의힘 동정</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>3) 국민의힘 동정</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>[뉴시스] "대출 숨통 틔워달라" 분출…난제 직면한 정부[부동산 새판 짜기③]</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/003/0014073765?sid=101</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>[국민일보] [임보혁 기자의 ‘예며들다’] 다섯 달란트와 한 달란트</t>
+          <t>[연합뉴스] [일문일답] 서울시의장 "한강버스, 출퇴근용 고집할지 운영 방향 따져야...</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001861669?sid=110</t>
+          <t>https://n.news.naver.com/mnews/article/001/0016201451?sid=100</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>[국민일보] “나무 심기는 선교”… 사막화 몽골을 푸르게 푸르게</t>
+          <t>[헤럴드경제] ‘190억 빚’ 임채무, 이번엔 발달장애인 위해 나선다</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001861664?sid=103</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002671773?sid=103</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] “서 회장도 박 노인도 67년 전 만난 샤일록이 낳았죠”</t>
+          <t>[매일경제] 8천만원車, 한국선 ‘반값’ 3천만원대...‘세계 최고’ 극찬받은 현대...</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/353/0000056049?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/009/0005708987?sid=103</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>[TV조선] [티조챗] 李대통령 언급한 낙태약 '미프진' 뭐길래…도입 놓고 공방 왜...</t>
+          <t>[연합뉴스] 이달 원화 절상률 주요국 1위…원/엔 1년8개월 만에 최저</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000627600?sid=100</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>[서울신문] “축구인들, 반성하고 각성해야”…기성용, 월드컵 조기 탈락에 쓴소리</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/081/0003662207?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/001/0016201440?sid=101</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>4) 경제 동정</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>4) 경제 동정</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>[머니투데이] 스테이블코인 '싫어요', 토큰화 '좋아요'…블록체인 활용에 다른 시각,...</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/008/0005387538?sid=101</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] [단독]'17조+α' AI 투자 몰리는 솔라시도..삼성 외 6곳 검토</t>
+          <t>[디지털타임스] 코웨이, 렌털 계정 1200만 눈앞…‘계정 경제’ 독주 굳힌다</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005387433?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/029/0003037521?sid=101</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] 中초원 살린 현대차, 경제도 잡아…"도시 떠난 주민이 돌아왔다"</t>
+          <t>[뉴스1] 북한 '텅스텐 특수'…중국 수출 규제로 '반사이익' 누려</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009065695?sid=104</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009066230?sid=100</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>[조선일보] [인터뷰] 전광우 "정년 연장, 재고용 방식으로 가면 청년층과 충돌 없어...</t>
+          <t>[파이낸셜뉴스] "챗GPT가 사란 대로 샀더니 대박"…AI 조언 듣고 주식한다고? [개미의 세...</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/053/0000060015?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005549616?sid=101</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] 농심 이어 오뚜기도 품었다…‘신선한 라면’ 맛볼 수 있는 이곳</t>
+          <t>[연합뉴스] 검찰도 '부동산 투기와 전쟁'…전국에 전담검사 지정·엄정 대응</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003538366?sid=102</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>[중앙일보] ‘차관급’ 광주특별시 부시장…2명 뽑는데 400건 추천 몰렸다</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003538364?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/001/0016201447?sid=102</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -455,14 +455,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>일일 정치 주요뉴스 7/19(일)</t>
+          <t>일일 정치 주요뉴스 7/20(월)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>(기준: 2026-07-18 22:00 ~ 2026-07-19 06:00)</t>
+          <t>(기준: 2026-07-19 22:00 ~ 2026-07-20 06:00)</t>
         </is>
       </c>
     </row>
@@ -476,96 +476,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] 與당권주자 메시지 경쟁 치열…김민석 '국정', 송영길 '실행', 정청래 '...</t>
+          <t>[데일리안] 장동혁 리더십 위기 속 '친장'의 명암…결집·이탈 기류 동시에</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014073763?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003112671?sid=100</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스] 임만균 서울시의장 "오세훈 시정 견제 강하게, 협력은 적극적으로"</t>
+          <t>[경향신문] ‘일주일 유예’ 김건희 24일 대법 선고…오세훈·최태원까지 법조계 슈...</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/001/0016201448?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/032/0003459095?sid=102</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[세계일보] 오세훈 ‘여론조사비 대납’ 의혹 22일 선고…주요 쟁점은?</t>
+          <t>[연합뉴스TV] [뉴스초점] 민주, 전대 '기탁금' 논란…장동혁, 연휴 내내 장외정치</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/022/0004144030?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/422/0000886658?sid=100</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[디지털타임스] 김민석 ‘적임론’·정청래 ‘동정론’·송영길 ‘정면돌파’… 첫 주말...</t>
+          <t>[디지털타임스] 김민석, “위장한 反明분열주의·신천지와의 대회전” 선언</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0003037511?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/029/0003037677?sid=100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[노컷뉴스] '尹체포방해' 나경원·김기현 부른 종합특검…성과 있을까</t>
+          <t>[노컷뉴스] 정청래의 '언더독' 전략…매번 '지는척' 이기는 방법</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004169562?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/079/0004169704?sid=100</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[디지털타임스] ‘친장동혁’ 조광한, 경기도당위원장 선거 출마 번복…“생각접어”</t>
+          <t>[서울신문] ‘장외 정치’ 외줄 타는 장동혁… 부정선거 주장·강성 지지층 밀착 행...</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0003037510?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/081/0003662367?sid=100</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스] "대안도 방법도 없다"…반장동혁, 張체제 사실상 방치 기류</t>
+          <t>[디지털타임스] 장동혁 “제헌절은 올공데이”… 안철수 “괴물 없고 국민 있더라”</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/001/0016201432?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/029/0003037673?sid=100</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[더팩트] [인터뷰] '비대위원장' 자처 조경태 "장동혁 대신 덧셈정치…한동훈 즉...</t>
+          <t>[한국일보] 박지현은 탈락, 송영길은 예외… 대통령까지 움직인 민주당 '불공정' 논...</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000517007?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000943071?sid=100</t>
         </is>
       </c>
     </row>
@@ -579,182 +579,194 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>[경향신문] 정청래 “어머니 저는 어떡해야 하나요···만나는 사람마다 ‘괜찮냐...</t>
+          <t>[동아일보] 김민석, 李 고향 안동서 ‘명심’ 강조… 정청래 “이해찬 부인이 후원...</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/033/0000051388?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003734927?sid=100</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>[KBS] 대전 찾은 김민석 전 총리 “당 바로 잡을 시점”</t>
+          <t>[문화일보] 張, 李대통령에 “김민석은 자기 편이라 믿나…착각도 유분수” 비난</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012220627?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/021/0002805525?sid=100</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>[더팩트] 채상병 순직 3주기…'첫 구속영장 기각' 특검 수사 고비</t>
+          <t>[KBS] 김민석·송영길 부산서 당심 공략…21일 예비경선</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000517008?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012220835?sid=100</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>[YTN] 후보등록 마친 민주 당권주자들...본격 당심 행보</t>
+          <t>[디지털타임스] “당직·공직선거 구별 못 하나”… 李대통령, 국힘 ‘당무개입’ 비판...</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/052/0002381274?sid=100</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+          <t>https://n.news.naver.com/mnews/article/029/0003037686?sid=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>[연합뉴스] "독일·일본은 검사 수사 안한다?…직접 수사권에 수사 지휘도"</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/001/0016202441?sid=102</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>3) 국민의힘 동정</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>[뉴시스] "대출 숨통 틔워달라" 분출…난제 직면한 정부[부동산 새판 짜기③]</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014073765?sid=101</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스] [일문일답] 서울시의장 "한강버스, 출퇴근용 고집할지 운영 방향 따져야...</t>
+          <t>[뉴시스] '안보실 인사개입' 윤재순·임종득 오늘 재판 마무리…특검 구형</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/001/0016201451?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014074763?sid=102</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>[헤럴드경제] ‘190억 빚’ 임채무, 이번엔 발달장애인 위해 나선다</t>
+          <t>[뉴스1] 반도체 호황이 부른 통화 긴축 유턴…내수·서민경제 '3高 직격탄'</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002671773?sid=103</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009067267?sid=101</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>[매일경제] 8천만원車, 한국선 ‘반값’ 3천만원대...‘세계 최고’ 극찬받은 현대...</t>
+          <t>[뉴스1] 삼전닉스 레버리지 4개월만에 '졸속 출시'…환율 못 잡고 주가 반토막</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/009/0005708987?sid=103</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009067270?sid=101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스] 이달 원화 절상률 주요국 1위…원/엔 1년8개월 만에 최저</t>
+          <t>[연합뉴스TV] 이 대통령, 당무개입 野 비판에 "최소한 상식 갖춰야"</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/001/0016201440?sid=101</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+          <t>https://n.news.naver.com/mnews/article/422/0000886645?sid=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>[서울신문] 檢 “보완수사하라” 6만건 돌려보냈는데… 경찰 미제도 10만건</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/081/0003662370?sid=102</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>4) 경제 동정</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>[머니투데이] 스테이블코인 '싫어요', 토큰화 '좋아요'…블록체인 활용에 다른 시각,...</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005387538?sid=101</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>[디지털타임스] 코웨이, 렌털 계정 1200만 눈앞…‘계정 경제’ 독주 굳힌다</t>
+          <t>[연합뉴스] 한경협 류진 "신산업 규제 '안 되는 것 빼고 다 되는' 식으로"</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0003037521?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/001/0016202449?sid=101</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] 북한 '텅스텐 특수'…중국 수출 규제로 '반사이익' 누려</t>
+          <t>[뉴시스] 류진 한경협 회장 "반도체 호황 이후 대비해야…규제 시스템 재설계 필...</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009066230?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014074751?sid=101</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>[파이낸셜뉴스] "챗GPT가 사란 대로 샀더니 대박"…AI 조언 듣고 주식한다고? [개미의 세...</t>
+          <t>[뉴스1] 류진 "4대 그룹 복귀 위해 끝까지 노력…좋을 때 물러나고 싶다"</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005549616?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009067241?sid=101</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스] 검찰도 '부동산 투기와 전쟁'…전국에 전담검사 지정·엄정 대응</t>
+          <t>[연합뉴스] '뷰 맛집' 입소문에 서울시청 하늘전망대 개방 2주간 7천명 발길</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/001/0016201447?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/001/0016202457?sid=102</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>[뉴시스] 내년 2월 임기만료 한경협 류진 회장 "4대그룹 회장단 복귀 공약 지킬 것...</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/003/0014074755?sid=101</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -455,14 +455,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>일일 정치 주요뉴스 7/20(월)</t>
+          <t>일일 정치 주요뉴스 7/21(화)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>(기준: 2026-07-19 22:00 ~ 2026-07-20 06:00)</t>
+          <t>(기준: 2026-07-20 22:00 ~ 2026-07-21 06:00)</t>
         </is>
       </c>
     </row>
@@ -476,96 +476,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[데일리안] 장동혁 리더십 위기 속 '친장'의 명암…결집·이탈 기류 동시에</t>
+          <t>[중앙일보] [단독] 이재명표 ‘공공 의대’ 최소 967억…위치는 이곳 가능성</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003112671?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003538911?sid=102</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[경향신문] ‘일주일 유예’ 김건희 24일 대법 선고…오세훈·최태원까지 법조계 슈...</t>
+          <t>[서울신문] 비당권파 시·도당위원장 대거 포진… 장동혁 ‘우군’이 없다</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/032/0003459095?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/081/0003662717?sid=100</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스TV] [뉴스초점] 민주, 전대 '기탁금' 논란…장동혁, 연휴 내내 장외정치</t>
+          <t>[뉴스1] 선고 하루 앞 오세훈 '정치 운명' 공방 격화…시정·대권 행보 기로</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/422/0000886658?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009069297?sid=102</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[디지털타임스] 김민석, “위장한 反明분열주의·신천지와의 대회전” 선언</t>
+          <t>[동아일보] 김민석 “반명 분열주의 심판해야”… 정청래 “집토끼 나가면 총선 불...</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0003037677?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003735255?sid=100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[노컷뉴스] 정청래의 '언더독' 전략…매번 '지는척' 이기는 방법</t>
+          <t>[머니투데이] 국힘 윤리위, 주중 회의 연다… 장동혁發 '징계 내전' 본격화</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004169704?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005388317?sid=100</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] ‘장외 정치’ 외줄 타는 장동혁… 부정선거 주장·강성 지지층 밀착 행...</t>
+          <t>[국민일보] “가치실종” vs “주류의식”… 순혈주의에 숨막힌 이재명의 길</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/081/0003662367?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001862096?sid=100</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[디지털타임스] 장동혁 “제헌절은 올공데이”… 안철수 “괴물 없고 국민 있더라”</t>
+          <t>[문화일보] ‘호남 민심’ 구애 나선 김민석 아내 이태린 여사</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0003037673?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/021/0002805798?sid=100</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[한국일보] 박지현은 탈락, 송영길은 예외… 대통령까지 움직인 민주당 '불공정' 논...</t>
+          <t>[YTN] 첫 합동연설회서 '표심 전쟁'...정청래 집중 견제</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000943071?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/052/0002382075?sid=100</t>
         </is>
       </c>
     </row>
@@ -579,60 +579,60 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 김민석, 李 고향 안동서 ‘명심’ 강조… 정청래 “이해찬 부인이 후원...</t>
+          <t>[경향신문] [단독]잠실 시위 현장 업무에 ‘긴급 심리지원’ 받은 경찰 19명…법적...</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003734927?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/032/0003459333?sid=102</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>[문화일보] 張, 李대통령에 “김민석은 자기 편이라 믿나…착각도 유분수” 비난</t>
+          <t>[경향신문] [속보]‘관저 이전 조작 감사’ 유병호 구속···법원 “증거인멸 염려...</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002805525?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/032/0003459327?sid=102</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>[KBS] 김민석·송영길 부산서 당심 공략…21일 예비경선</t>
+          <t>[연합뉴스TV] 리얼미터 "이 대통령 지지도 48.4%…소폭 하락"</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012220835?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/422/0000887036?sid=100</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>[디지털타임스] “당직·공직선거 구별 못 하나”… 李대통령, 국힘 ‘당무개입’ 비판...</t>
+          <t>[노컷뉴스] 수사권 폐지해도 남는 '檢기소독점'…독일의 견제장치는?</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0003037686?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/079/0004170139?sid=102</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스] "독일·일본은 검사 수사 안한다?…직접 수사권에 수사 지휘도"</t>
+          <t>[연합뉴스] 與, '보완수사권 폐지' 놓고 전문가 정책의총…"논의 심화"</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/001/0016202441?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/001/0016204711?sid=100</t>
         </is>
       </c>
     </row>
@@ -646,60 +646,60 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] '안보실 인사개입' 윤재순·임종득 오늘 재판 마무리…특검 구형</t>
+          <t>[한국일보] [단독] 종합특검, '관저 사전답사' 김건희·윤한홍·21그램 동선 포착…...</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014074763?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000943376?sid=102</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] 반도체 호황이 부른 통화 긴축 유턴…내수·서민경제 '3高 직격탄'</t>
+          <t>[노컷뉴스] 오세훈, 부동산 대토론회 참석 불발…김용범 회동으로 갈음</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009067267?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/079/0004170138?sid=100</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] 삼전닉스 레버리지 4개월만에 '졸속 출시'…환율 못 잡고 주가 반토막</t>
+          <t>[세계일보] 李, 분당 아파트 매각… 野 “17억 근저당 꼼수거래”</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009067270?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/022/0004144547?sid=100</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스TV] 이 대통령, 당무개입 野 비판에 "최소한 상식 갖춰야"</t>
+          <t>[뉴스1] 꺼지지 않는 신용대출 증가세…"고점 물린 개미들, 상환 여유도 없어"</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/422/0000886645?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009069329?sid=101</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 檢 “보완수사하라” 6만건 돌려보냈는데… 경찰 미제도 10만건</t>
+          <t>[한국일보] "대구 핵심시설 품은 도시철도 4호선... 재검토는 다각도로, 추진은 속도...</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/081/0003662370?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000943387?sid=102</t>
         </is>
       </c>
     </row>
@@ -713,60 +713,60 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스] 한경협 류진 "신산업 규제 '안 되는 것 빼고 다 되는' 식으로"</t>
+          <t>[서울신문] [단독] 경찰 ‘순환인사 확대’ 반발 확산… 직협, 집회·수사경과 반납...</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/001/0016202449?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/081/0003662721?sid=102</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] 류진 한경협 회장 "반도체 호황 이후 대비해야…규제 시스템 재설계 필...</t>
+          <t>[한국일보] [단독] '쿠팡이츠'서 온 팀장님, 전 회사 자료로 '땡겨요' 만들었나</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014074751?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000943384?sid=102</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] 류진 "4대 그룹 복귀 위해 끝까지 노력…좋을 때 물러나고 싶다"</t>
+          <t>[동아일보] [단독]주력사업 부진에… 돈 안되는 ‘미래 먹거리’ 손턴다</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009067241?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003735202?sid=101</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스] '뷰 맛집' 입소문에 서울시청 하늘전망대 개방 2주간 7천명 발길</t>
+          <t>[뉴시스] "지금 안 사면 늦는다"…전세난이 키운 서울 집값 악순환</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/001/0016202457?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014077149?sid=101</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] 내년 2월 임기만료 한경협 류진 회장 "4대그룹 회장단 복귀 공약 지킬 것...</t>
+          <t>[머니투데이] '저가 공세' 중국 보고 있나...AI 올라탄 'K철강', 수출액 들썩</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014074755?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005388350?sid=101</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00999999"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -71,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -80,6 +85,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -476,96 +482,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] [단독] 이재명표 ‘공공 의대’ 최소 967억…위치는 이곳 가능성</t>
+          <t>[연합뉴스TV] 다시 거세진 장맛비…수도권 출근길 '물폭탄' 주의보 [7월 21일 AI PICK]</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003538911?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/422/0000887028?sid=100</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 비당권파 시·도당위원장 대거 포진… 장동혁 ‘우군’이 없다</t>
+          <t>[YTN] 정점식-이준석 오찬 회동...대여투쟁 공조 논의 전망</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/081/0003662717?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/052/0002382094?sid=100</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] 선고 하루 앞 오세훈 '정치 운명' 공방 격화…시정·대권 행보 기로</t>
+          <t>[서울신문] 여야, 원 구성은 뒷전… 종합특검 연장법 상정에 ‘필버’ 충돌</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009069297?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/081/0003662718?sid=100</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 김민석 “반명 분열주의 심판해야”… 정청래 “집토끼 나가면 총선 불...</t>
+          <t>[중앙일보] “씰 데 없는 소리 하고 있어!” YS 욱하게 한 초선 MB 질문</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003735255?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003538908?sid=100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] 국힘 윤리위, 주중 회의 연다… 장동혁發 '징계 내전' 본격화</t>
+          <t>[뉴스1] '종합특검 연장법' 오늘 국회 통과 전망…野 필리버스터, 與 종결 대응</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005388317?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009069322?sid=100</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[국민일보] “가치실종” vs “주류의식”… 순혈주의에 숨막힌 이재명의 길</t>
+          <t>[노컷뉴스] "오롯이 시민의 마음으로"…장정순 용인시의회 의장의 '시민 정치'</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001862096?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/079/0004170142?sid=102</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[문화일보] ‘호남 민심’ 구애 나선 김민석 아내 이태린 여사</t>
+          <t>[동아일보] 후반기 국회 시작부터 충돌… 민주 “특검 연장” 국힘 ‘필버’ 맞불</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002805798?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003735258?sid=100</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[YTN] 첫 합동연설회서 '표심 전쟁'...정청래 집중 견제</t>
+          <t>[머니투데이] 원구성도 못한채 강대강 대치… 후반기 첫 본회의부터 '필버'</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/052/0002382075?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005388302?sid=100</t>
         </is>
       </c>
     </row>
@@ -577,196 +583,90 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>[경향신문] [단독]잠실 시위 현장 업무에 ‘긴급 심리지원’ 받은 경찰 19명…법적...</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/032/0003459333?sid=102</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>[경향신문] [속보]‘관저 이전 조작 감사’ 유병호 구속···법원 “증거인멸 염려...</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/032/0003459327?sid=102</t>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>(해당 시간대 기사 없음)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>[연합뉴스TV] 리얼미터 "이 대통령 지지도 48.4%…소폭 하락"</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/422/0000887036?sid=100</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>3) 국민의힘 동정</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>[노컷뉴스] 수사권 폐지해도 남는 '檢기소독점'…독일의 견제장치는?</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004170139?sid=102</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>[연합뉴스] 與, '보완수사권 폐지' 놓고 전문가 정책의총…"논의 심화"</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/001/0016204711?sid=100</t>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>(해당 시간대 기사 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>4) 경제 동정</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>3) 국민의힘 동정</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>[이데일리] [속보]뉴욕증시 또 하락…'중동 불안'에 빅테크 실적 경계감까지</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/018/0006333457?sid=101</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>[한국일보] [단독] 종합특검, '관저 사전답사' 김건희·윤한홍·21그램 동선 포착…...</t>
+          <t>[디지털타임스] 美 42개 주서 ‘AI 데이터 센터’ 반대 시위…“전기·물 사용량 높여 부...</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000943376?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/029/0003037916?sid=101</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>[노컷뉴스] 오세훈, 부동산 대토론회 참석 불발…김용범 회동으로 갈음</t>
+          <t>[이데일리] 중동 전운에 숨죽인 뉴욕증시…빅테크 실적 시즌 '시험대' [월스트리트...</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004170138?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006333472?sid=101</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>[세계일보] 李, 분당 아파트 매각… 野 “17억 근저당 꼼수거래”</t>
+          <t>[이데일리] "AI 투자 증가세 꺾여"…"성장률 둔화와 피크아웃 구분해야"</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/022/0004144547?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006333461?sid=101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] 꺼지지 않는 신용대출 증가세…"고점 물린 개미들, 상환 여유도 없어"</t>
+          <t>[서울경제] AI 투자 경쟁의 그림자…미국 빅테크 ‘숨은 빚’ 2455조원</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009069329?sid=101</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>[한국일보] "대구 핵심시설 품은 도시철도 4호선... 재검토는 다각도로, 추진은 속도...</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000943387?sid=102</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>4) 경제 동정</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>[서울신문] [단독] 경찰 ‘순환인사 확대’ 반발 확산… 직협, 집회·수사경과 반납...</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/081/0003662721?sid=102</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>[한국일보] [단독] '쿠팡이츠'서 온 팀장님, 전 회사 자료로 '땡겨요' 만들었나</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000943384?sid=102</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>[동아일보] [단독]주력사업 부진에… 돈 안되는 ‘미래 먹거리’ 손턴다</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003735202?sid=101</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>[뉴시스] "지금 안 사면 늦는다"…전세난이 키운 서울 집값 악순환</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014077149?sid=101</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>[머니투데이] '저가 공세' 중국 보고 있나...AI 올라탄 'K철강', 수출액 들썩</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005388350?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004643324?sid=104</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -482,96 +482,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스TV] 다시 거세진 장맛비…수도권 출근길 '물폭탄' 주의보 [7월 21일 AI PICK]</t>
+          <t>[YTN] 정점식-이준석 오찬 회동...대여투쟁 공조 논의 전망</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/422/0000887028?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/052/0002382094?sid=100</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[YTN] 정점식-이준석 오찬 회동...대여투쟁 공조 논의 전망</t>
+          <t>[서울신문] 여야, 원 구성은 뒷전… 종합특검 연장법 상정에 ‘필버’ 충돌</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/052/0002382094?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/081/0003662718?sid=100</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 여야, 원 구성은 뒷전… 종합특검 연장법 상정에 ‘필버’ 충돌</t>
+          <t>[중앙일보] “씰 데 없는 소리 하고 있어!” YS 욱하게 한 초선 MB 질문</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/081/0003662718?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003538908?sid=100</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] “씰 데 없는 소리 하고 있어!” YS 욱하게 한 초선 MB 질문</t>
+          <t>[뉴스1] '종합특검 연장법' 오늘 국회 통과 전망…野 필리버스터, 與 종결 대응</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003538908?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009069322?sid=100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] '종합특검 연장법' 오늘 국회 통과 전망…野 필리버스터, 與 종결 대응</t>
+          <t>[동아일보] 후반기 국회 시작부터 충돌… 민주 “특검 연장” 국힘 ‘필버’ 맞불</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009069322?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003735258?sid=100</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[노컷뉴스] "오롯이 시민의 마음으로"…장정순 용인시의회 의장의 '시민 정치'</t>
+          <t>[머니투데이] 원구성도 못한채 강대강 대치… 후반기 첫 본회의부터 '필버'</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004170142?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005388302?sid=100</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 후반기 국회 시작부터 충돌… 민주 “특검 연장” 국힘 ‘필버’ 맞불</t>
+          <t>[YTN] 종합특검 연장법 '필버' 대치...오늘 통과 불투명?</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003735258?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/052/0002382121?sid=100</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] 원구성도 못한채 강대강 대치… 후반기 첫 본회의부터 '필버'</t>
+          <t>[서울경제] [기자의 눈] 단일종목 레버리지가 소환한 ‘라임의 추억’</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005388302?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004643312?sid=101</t>
         </is>
       </c>
     </row>
@@ -625,48 +625,48 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>[디지털타임스] 美 42개 주서 ‘AI 데이터 센터’ 반대 시위…“전기·물 사용량 높여 부...</t>
+          <t>[뉴시스] 1500원대 무너진 원·달러…强달러 여지는 '여전'</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0003037916?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014077136?sid=101</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>[이데일리] 중동 전운에 숨죽인 뉴욕증시…빅테크 실적 시즌 '시험대' [월스트리트...</t>
+          <t>[뉴시스] 日서 먼저 오른 아이폰값…'200만원 아이폰' 한국도 눈앞</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006333472?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014077151?sid=105</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>[이데일리] "AI 투자 증가세 꺾여"…"성장률 둔화와 피크아웃 구분해야"</t>
+          <t>[디지털타임스] 美 42개 주서 ‘AI 데이터 센터’ 반대 시위…“전기·물 사용량 높여 부...</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006333461?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/029/0003037916?sid=101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>[서울경제] AI 투자 경쟁의 그림자…미국 빅테크 ‘숨은 빚’ 2455조원</t>
+          <t>[뉴시스] V자 반등 기대했는데 'L자' 늪?…다시 떠오르는 '박스피' 우려</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004643324?sid=104</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014077142?sid=101</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/052/0002382094?sid=100</t>
+          <t>https://tinyurl.com/27dn77nr</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/081/0003662718?sid=100</t>
+          <t>https://tinyurl.com/29uxej5u</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003538908?sid=100</t>
+          <t>https://tinyurl.com/2cryc5yh</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009069322?sid=100</t>
+          <t>https://tinyurl.com/2xlpprzn</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003735258?sid=100</t>
+          <t>https://tinyurl.com/2yg769co</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005388302?sid=100</t>
+          <t>https://tinyurl.com/2y2ggyw7</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/052/0002382121?sid=100</t>
+          <t>https://tinyurl.com/2623uotd</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004643312?sid=101</t>
+          <t>https://tinyurl.com/27h4dyan</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006333457?sid=101</t>
+          <t>https://tinyurl.com/28bzqg4o</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014077136?sid=101</t>
+          <t>https://tinyurl.com/27us38o7</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014077151?sid=105</t>
+          <t>https://tinyurl.com/223q84xx</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0003037916?sid=101</t>
+          <t>https://tinyurl.com/23uqr7ht</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014077142?sid=101</t>
+          <t>https://tinyurl.com/233cdpns</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,11 +50,6 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00999999"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -76,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -85,7 +80,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -451,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -461,14 +455,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>일일 정치 주요뉴스 7/21(화)</t>
+          <t>일일 정치 주요뉴스 7/22(수)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>(기준: 2026-07-20 22:00 ~ 2026-07-21 06:00)</t>
+          <t>(기준: 2026-07-21 22:00 ~ 2026-07-22 06:00)</t>
         </is>
       </c>
     </row>
@@ -482,96 +476,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[YTN] 정점식-이준석 오찬 회동...대여투쟁 공조 논의 전망</t>
+          <t>[연합뉴스] '명태균 여론조사 대납 의혹' 오세훈 시장, 오늘 1심 선고</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/27dn77nr</t>
+          <t>https://tinyurl.com/287f5y34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 여야, 원 구성은 뒷전… 종합특검 연장법 상정에 ‘필버’ 충돌</t>
+          <t>[서울경제] 오세훈 운명의 날…‘여론조사 비용 대납 의혹’ 오늘 1심 선고</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/29uxej5u</t>
+          <t>https://tinyurl.com/2d72joxa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] “씰 데 없는 소리 하고 있어!” YS 욱하게 한 초선 MB 질문</t>
+          <t>[뉴스1] 오세훈 '명태균 여론조사비 대납' 1심 오늘 선고</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2cryc5yh</t>
+          <t>https://tinyurl.com/24fwrxdg</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] '종합특검 연장법' 오늘 국회 통과 전망…野 필리버스터, 與 종결 대응</t>
+          <t>[디지털타임스] ‘여론조사비 대납 의혹’ 오세훈, 22일 1심 선고…녹화 중계도 진행</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2xlpprzn</t>
+          <t>https://tinyurl.com/29fk8nam</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 후반기 국회 시작부터 충돌… 민주 “특검 연장” 국힘 ‘필버’ 맞불</t>
+          <t>[연합뉴스TV] '여론조사 대납 의혹' 오세훈…오늘 법원 첫 판단</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2yg769co</t>
+          <t>https://tinyurl.com/28l5s8gl</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] 원구성도 못한채 강대강 대치… 후반기 첫 본회의부터 '필버'</t>
+          <t>[TV조선] '여론조사비 대납' 오세훈 오늘 1심 선고…구형은 징역 1년 6개월</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2y2ggyw7</t>
+          <t>https://tinyurl.com/2xl3a63w</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[YTN] 종합특검 연장법 '필버' 대치...오늘 통과 불투명?</t>
+          <t>[KBS] 오세훈 ‘여론조사비 대납’ 오늘 선고…징역 1년 6개월 구형</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2623uotd</t>
+          <t>https://tinyurl.com/2akb6zvb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[서울경제] [기자의 눈] 단일종목 레버리지가 소환한 ‘라임의 추억’</t>
+          <t>[YTN] '여론조사 대납' 오세훈 오늘 1심 선고...징역 1년 6개월 구형</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/27h4dyan</t>
+          <t>https://tinyurl.com/2c97xfjd</t>
         </is>
       </c>
     </row>
@@ -583,90 +577,196 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>(해당 시간대 기사 없음)</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>[서울신문] 정청래 차량 파손에 ‘신천지 개입설’까지… 선 넘는 與전대</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/234dhhj2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>[노컷뉴스] 김민석은 왜 '신천지'를 언급할까…숨겨진 전략은</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/2yyrxdhg</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>[뉴시스] 오세훈 오늘 '여론조사비 대납 혐의' 1심 선고…구형 징역 1년6개월</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/29c62tnq</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>[뉴시스] 與 전대, 김민석·정청래 충돌 격화…'反明' 설전에 '4년 전 이 대통령 ...</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/257xylkl</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>[동아일보] 김민석, ‘신천지 전대 개입설’ 제기… 정청래 “황당한 네거티브”</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/23z47owj</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>3) 국민의힘 동정</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>(해당 시간대 기사 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>4) 경제 동정</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>[이데일리] [속보]뉴욕증시 또 하락…'중동 불안'에 빅테크 실적 경계감까지</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/28bzqg4o</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] 1500원대 무너진 원·달러…强달러 여지는 '여전'</t>
+          <t>[머니투데이] '명태균 여론조사 대납' 오세훈 1심 선고… 구형은 징역 1년6개월</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/27us38o7</t>
+          <t>https://tinyurl.com/27geucsw</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] 日서 먼저 오른 아이폰값…'200만원 아이폰' 한국도 눈앞</t>
+          <t>[디지털타임스] “배우자가 무슨 역할 했나”…우원식 해외출장 14회 모두 동행·82억 집...</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/223q84xx</t>
+          <t>https://tinyurl.com/2ar6z653</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>[디지털타임스] 美 42개 주서 ‘AI 데이터 센터’ 반대 시위…“전기·물 사용량 높여 부...</t>
+          <t>[JIBS] "노인 비하, 당게 한동훈 따라갈 수 없다" 발언 장예찬 무혐의.. 張 "검...</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/23uqr7ht</t>
+          <t>https://tinyurl.com/25rj3g7u</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] V자 반등 기대했는데 'L자' 늪?…다시 떠오르는 '박스피' 우려</t>
+          <t>[더팩트] '장동혁 사퇴론' 동력 상실?…잠잠해진 진짜 이유는</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/233cdpns</t>
+          <t>https://tinyurl.com/25x4nydt</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>[더팩트] '강경 징계' 역풍 기대한 한동훈?…국힘, '본보기 카드' 무게 두나</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/2b7u8dzk</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>4) 경제 동정</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>[한국일보] 코스닥 역주행에 커지는 '상폐 공포'... 이재명 취임 전으로 회귀</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/2233pfz9</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>[이데일리] [단독]'따릉이 정보유출' 대형사고에도…서울시설공단 이사장 연임 논란</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/2adfrvoj</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>[동아일보] [단독]노벨상 교수 “AI發 생산성 향상, 고용 창출까진 시차… 충격 불...</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/2c7ge29f</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>[국민일보] [단독] “AI로 2030 다시 잡아라”… ‘국민 첫 차’ 아반떼 재시동</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/24asyqgm</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>[더팩트] [단독] "김일성 품, 진정한 조국"…조총련 의장 자서전 입수</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/29afggds</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/287f5y34</t>
+          <t>https://n.news.naver.com/mnews/article/001/0016207102?sid=102</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2d72joxa</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004643754?sid=102</t>
         </is>
       </c>
     </row>
@@ -505,7 +505,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/24fwrxdg</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009071466?sid=102</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/29fk8nam</t>
+          <t>https://n.news.naver.com/mnews/article/029/0003038158?sid=102</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/28l5s8gl</t>
+          <t>https://n.news.naver.com/mnews/article/422/0000887462?sid=102</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2xl3a63w</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000628394?sid=102</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2akb6zvb</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012222492?sid=102</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2c97xfjd</t>
+          <t>https://n.news.naver.com/mnews/article/052/0002382665?sid=102</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 정청래 차량 파손에 ‘신천지 개입설’까지… 선 넘는 與전대</t>
+          <t>[한겨레] 우원식 “민주당, 양극화 토론 한번을 안 해…중산층·서민 정당 맞나”</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/234dhhj2</t>
+          <t>https://n.news.naver.com/mnews/article/028/0002815160?sid=100</t>
         </is>
       </c>
     </row>
@@ -596,43 +596,43 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2yyrxdhg</t>
+          <t>https://n.news.naver.com/mnews/article/079/0004170634?sid=100</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] 오세훈 오늘 '여론조사비 대납 혐의' 1심 선고…구형 징역 1년6개월</t>
+          <t>[서울신문] 정청래 차량 파손에 ‘신천지 개입설’까지… 선 넘는 與전대</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/29c62tnq</t>
+          <t>https://n.news.naver.com/mnews/article/081/0003663208?sid=100</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] 與 전대, 김민석·정청래 충돌 격화…'反明' 설전에 '4년 전 이 대통령 ...</t>
+          <t>[뉴시스] 오세훈 오늘 '여론조사비 대납 혐의' 1심 선고…구형 징역 1년6개월</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/257xylkl</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014079773?sid=102</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 김민석, ‘신천지 전대 개입설’ 제기… 정청래 “황당한 네거티브”</t>
+          <t>[뉴시스] 與 전대, 김민석·정청래 충돌 격화…'反明' 설전에 '4년 전 이 대통령 ...</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/23z47owj</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014079777?sid=100</t>
         </is>
       </c>
     </row>
@@ -646,12 +646,12 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] '명태균 여론조사 대납' 오세훈 1심 선고… 구형은 징역 1년6개월</t>
+          <t>[머니투데이] 오세훈, 여론조사 대납 1심 선고 '운명의 날'…구형은 '시장직 박탈형'</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/27geucsw</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005388961?sid=102</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2ar6z653</t>
+          <t>https://n.news.naver.com/mnews/article/029/0003038151?sid=100</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/25rj3g7u</t>
+          <t>https://n.news.naver.com/mnews/article/661/0000080295?sid=100</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/25x4nydt</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000517842?sid=100</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2b7u8dzk</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000517843?sid=100</t>
         </is>
       </c>
     </row>
@@ -718,19 +718,19 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2233pfz9</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000943610?sid=101</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>[이데일리] [단독]'따릉이 정보유출' 대형사고에도…서울시설공단 이사장 연임 논란</t>
+          <t>[이데일리] [단독]'따릉이 정보유출'에도…서울시설공단 이사장 연임 논란</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2adfrvoj</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006334250?sid=100</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2c7ge29f</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003735595?sid=102</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/24asyqgm</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001862350?sid=101</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/29afggds</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000517840?sid=100</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/001/0016207102?sid=102</t>
+          <t>https://n.news.naver.com/article/001/0016207102</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004643754?sid=102</t>
+          <t>https://n.news.naver.com/article/011/0004643754</t>
         </is>
       </c>
     </row>
@@ -505,7 +505,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009071466?sid=102</t>
+          <t>https://n.news.naver.com/article/421/0009071466</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0003038158?sid=102</t>
+          <t>https://n.news.naver.com/article/029/0003038158</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/422/0000887462?sid=102</t>
+          <t>https://n.news.naver.com/article/422/0000887462</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000628394?sid=102</t>
+          <t>https://n.news.naver.com/article/448/0000628394</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012222492?sid=102</t>
+          <t>https://n.news.naver.com/article/056/0012222492</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/052/0002382665?sid=102</t>
+          <t>https://n.news.naver.com/article/052/0002382665</t>
         </is>
       </c>
     </row>
@@ -584,55 +584,55 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/028/0002815160?sid=100</t>
+          <t>https://n.news.naver.com/article/028/0002815160</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>[노컷뉴스] 김민석은 왜 '신천지'를 언급할까…숨겨진 전략은</t>
+          <t>[서울신문] 정청래 차량 파손에 ‘신천지 개입설’까지… 선 넘는 與전대</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004170634?sid=100</t>
+          <t>https://n.news.naver.com/article/081/0003663208</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 정청래 차량 파손에 ‘신천지 개입설’까지… 선 넘는 與전대</t>
+          <t>[노컷뉴스] 김민석은 왜 '신천지'를 언급할까…숨겨진 전략은</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/081/0003663208?sid=100</t>
+          <t>https://n.news.naver.com/article/079/0004170634</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] 오세훈 오늘 '여론조사비 대납 혐의' 1심 선고…구형 징역 1년6개월</t>
+          <t>[뉴시스] 與 전대, 김민석·정청래 충돌 격화…'反明' 설전에 '4년 전 이 대통령 ...</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014079773?sid=102</t>
+          <t>https://n.news.naver.com/article/003/0014079777</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] 與 전대, 김민석·정청래 충돌 격화…'反明' 설전에 '4년 전 이 대통령 ...</t>
+          <t>[뉴시스] 오세훈 오늘 '여론조사비 대납 혐의' 1심 선고…구형 징역 1년6개월</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014079777?sid=100</t>
+          <t>https://n.news.naver.com/article/003/0014079773</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005388961?sid=102</t>
+          <t>https://n.news.naver.com/article/008/0005388961</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0003038151?sid=100</t>
+          <t>https://n.news.naver.com/article/029/0003038151</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/661/0000080295?sid=100</t>
+          <t>https://n.news.naver.com/article/661/0000080295</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000517842?sid=100</t>
+          <t>https://n.news.naver.com/article/629/0000517842</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000517843?sid=100</t>
+          <t>https://n.news.naver.com/article/629/0000517843</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000943610?sid=101</t>
+          <t>https://n.news.naver.com/article/469/0000943610</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006334250?sid=100</t>
+          <t>https://n.news.naver.com/article/018/0006334250</t>
         </is>
       </c>
     </row>
@@ -742,31 +742,31 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003735595?sid=102</t>
+          <t>https://n.news.naver.com/article/020/0003735595</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>[국민일보] [단독] “AI로 2030 다시 잡아라”… ‘국민 첫 차’ 아반떼 재시동</t>
+          <t>[더팩트] [단독] "김일성 품, 진정한 조국"…조총련 의장 자서전 입수</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001862350?sid=101</t>
+          <t>https://n.news.naver.com/article/629/0000517840</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>[더팩트] [단독] "김일성 품, 진정한 조국"…조총련 의장 자서전 입수</t>
+          <t>[머니투데이] [광화문]이재명 정부의 부동산 클라이맥스</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000517840?sid=100</t>
+          <t>https://n.news.naver.com/article/008/0005388944</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -749,24 +749,24 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>[더팩트] [단독] "김일성 품, 진정한 조국"…조총련 의장 자서전 입수</t>
+          <t>[머니투데이] [광화문]이재명 정부의 부동산 클라이맥스</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/629/0000517840</t>
+          <t>https://n.news.naver.com/article/008/0005388944</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] [광화문]이재명 정부의 부동산 클라이맥스</t>
+          <t>[머니투데이] "하녀처럼 부리던 여교사 구타" 췌장 파열→사망...종교인 탈 쓴 악마 짓...</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/008/0005388944</t>
+          <t>https://n.news.naver.com/article/008/0005388976</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -455,14 +455,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>일일 정치 주요뉴스 7/22(수)</t>
+          <t>일일 정치 주요뉴스 7/23(목)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>(기준: 2026-07-21 22:00 ~ 2026-07-22 06:00)</t>
+          <t>(기준: 2026-07-22 22:00 ~ 2026-07-23 06:00)</t>
         </is>
       </c>
     </row>
@@ -476,96 +476,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스] '명태균 여론조사 대납 의혹' 오세훈 시장, 오늘 1심 선고</t>
+          <t>[연합뉴스TV] '여론조사 대납' 오세훈 1심 당선무효형…벌금 1천만원</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/001/0016207102</t>
+          <t>https://n.news.naver.com/article/422/0000887871</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[서울경제] 오세훈 운명의 날…‘여론조사 비용 대납 의혹’ 오늘 1심 선고</t>
+          <t>[중앙일보] “100% 투표” vs “아프다”…김민석·정청래의 ‘깜깜이 당심’ 공략...</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/011/0004643754</t>
+          <t>https://n.news.naver.com/article/025/0003539514</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] 오세훈 '명태균 여론조사비 대납' 1심 오늘 선고</t>
+          <t>[조선일보] 오세훈 ‘여론조사 대납’ 1심서 시장직 상실형</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/421/0009071466</t>
+          <t>https://n.news.naver.com/article/023/0003989127</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[디지털타임스] ‘여론조사비 대납 의혹’ 오세훈, 22일 1심 선고…녹화 중계도 진행</t>
+          <t>[조선일보] 오세훈 "1심 판결 중대한 오류…상급심서 바로잡힐 것"</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/029/0003038158</t>
+          <t>https://n.news.naver.com/article/053/0000060134</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스TV] '여론조사 대납 의혹' 오세훈…오늘 법원 첫 판단</t>
+          <t>[SBS] '여론조사 대납' 오세훈 1심 '시장직 상실형' 선고</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/422/0000887462</t>
+          <t>https://n.news.naver.com/article/055/0001374645</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[TV조선] '여론조사비 대납' 오세훈 오늘 1심 선고…구형은 징역 1년 6개월</t>
+          <t>[MBC] 오세훈 벌금 '1천만 원'‥서울시장직 '상실형'</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/448/0000628394</t>
+          <t>https://n.news.naver.com/article/214/0001513316</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[KBS] 오세훈 ‘여론조사비 대납’ 오늘 선고…징역 1년 6개월 구형</t>
+          <t>[KBS] “나경원에 패하자 명태균 찾았다”…오세훈 주장 모두 배척</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/056/0012222492</t>
+          <t>https://n.news.naver.com/article/056/0012223316</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[YTN] '여론조사 대납' 오세훈 오늘 1심 선고...징역 1년 6개월 구형</t>
+          <t>[KBS] 오세훈 1심 벌금 1천만 원…“명태균 여론조사 대납 인정”</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/052/0002382665</t>
+          <t>https://n.news.naver.com/article/056/0012223315</t>
         </is>
       </c>
     </row>
@@ -579,60 +579,60 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>[한겨레] 우원식 “민주당, 양극화 토론 한번을 안 해…중산층·서민 정당 맞나”</t>
+          <t>[서울신문] 유시민 “어물전 썩은 내” 김민석 “헛예언은 필패”</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/028/0002815160</t>
+          <t>https://n.news.naver.com/article/081/0003663741</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 정청래 차량 파손에 ‘신천지 개입설’까지… 선 넘는 與전대</t>
+          <t>[동아일보] 송영길 “신천지, 내게도 접근” 정청래 “전대 개입 근거 밝혀라”</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/081/0003663208</t>
+          <t>https://n.news.naver.com/article/020/0003735899</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>[노컷뉴스] 김민석은 왜 '신천지'를 언급할까…숨겨진 전략은</t>
+          <t>[한국일보] 정청래 "10년 만에 가장 분노"... 연일 '신천지 설' 띄우는 김민석에 경...</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/079/0004170634</t>
+          <t>https://n.news.naver.com/article/469/0000943817</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] 與 전대, 김민석·정청래 충돌 격화…'反明' 설전에 '4년 전 이 대통령 ...</t>
+          <t>[한국일보] "여당 무죄·야당 유죄" 오세훈 선고에 당혹스러운 야권... 보수 '구심점...</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/003/0014079777</t>
+          <t>https://n.news.naver.com/article/469/0000943822</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] 오세훈 오늘 '여론조사비 대납 혐의' 1심 선고…구형 징역 1년6개월</t>
+          <t>[JIBS] 국힘 '李 근저당' 공세.. 민주 "장동혁 6채는?" 역공</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/003/0014079773</t>
+          <t>https://n.news.naver.com/article/661/0000080369</t>
         </is>
       </c>
     </row>
@@ -646,60 +646,60 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] 오세훈, 여론조사 대납 1심 선고 '운명의 날'…구형은 '시장직 박탈형'</t>
+          <t>[연합뉴스TV] "오세훈, 여론조사 의뢰할 동기 있어"…명태균 진술 인정</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/008/0005388961</t>
+          <t>https://n.news.naver.com/article/422/0000887873</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>[디지털타임스] “배우자가 무슨 역할 했나”…우원식 해외출장 14회 모두 동행·82억 집...</t>
+          <t>[노컷뉴스] 윤석열·오세훈 유죄…'명태균 게이트' 법원 판단 공통점</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/029/0003038151</t>
+          <t>https://n.news.naver.com/article/079/0004171092</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>[JIBS] "노인 비하, 당게 한동훈 따라갈 수 없다" 발언 장예찬 무혐의.. 張 "검...</t>
+          <t>[노컷뉴스] "올 것이 왔다"…오세훈 1심 당선무효형에 국힘 '술렁'</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/661/0000080295</t>
+          <t>https://n.news.naver.com/article/079/0004171089</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>[더팩트] '장동혁 사퇴론' 동력 상실?…잠잠해진 진짜 이유는</t>
+          <t>[서울신문] “장동혁 단순 비판, 징계 대상 아냐”… 국힘 윤리위 ‘정적 견제’ 논...</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/629/0000517842</t>
+          <t>https://n.news.naver.com/article/081/0003663738</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>[더팩트] '강경 징계' 역풍 기대한 한동훈?…국힘, '본보기 카드' 무게 두나</t>
+          <t>[서울신문] ‘여론조사비 대납’ 1심, 오세훈 벌금 1000만원</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/629/0000517843</t>
+          <t>https://n.news.naver.com/article/081/0003663730</t>
         </is>
       </c>
     </row>
@@ -713,60 +713,60 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>[한국일보] 코스닥 역주행에 커지는 '상폐 공포'... 이재명 취임 전으로 회귀</t>
+          <t>[뉴스1] 'G3·야간경제' 시험대 오른 오세훈…15년 전엔 사퇴 뒤 사업 제동</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/469/0000943610</t>
+          <t>https://n.news.naver.com/article/421/0009073865</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>[이데일리] [단독]'따릉이 정보유출'에도…서울시설공단 이사장 연임 논란</t>
+          <t>[한국일보] 오세훈 '사법 리스크', 서울 재개발도 흔들까... '재건축·야간경제' 등...</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/018/0006334250</t>
+          <t>https://n.news.naver.com/article/469/0000943823</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] [단독]노벨상 교수 “AI發 생산성 향상, 고용 창출까진 시차… 충격 불...</t>
+          <t>[경향신문] [단독]“미프진 구해요” 댓글에 달린 ‘이곳’…법 사라진 곳에 쏟아진...</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/020/0003735595</t>
+          <t>https://n.news.naver.com/article/032/0003459838</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] [광화문]이재명 정부의 부동산 클라이맥스</t>
+          <t>[한겨레] [단독] ‘인천공항 최장 구금’ 피해자 난민신청 6년 만에 ‘체류 허가...</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/008/0005388944</t>
+          <t>https://n.news.naver.com/article/028/0002815341</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] "하녀처럼 부리던 여교사 구타" 췌장 파열→사망...종교인 탈 쓴 악마 짓...</t>
+          <t>[뉴시스] 4대 금융, 실적 시즌 개막…'가계대출 빗장'에도 11조 순익 전망</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/008/0005388976</t>
+          <t>https://n.news.naver.com/article/003/0014082510</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -455,14 +455,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>일일 정치 주요뉴스 7/23(목)</t>
+          <t>일일 정치 주요뉴스 7/24(금)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>(기준: 2026-07-22 22:00 ~ 2026-07-23 06:00)</t>
+          <t>(기준: 2026-07-23 22:00 ~ 2026-07-24 06:00)</t>
         </is>
       </c>
     </row>
@@ -476,96 +476,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스TV] '여론조사 대납' 오세훈 1심 당선무효형…벌금 1천만원</t>
+          <t>[중앙일보] 오세훈 유죄 다음날…대법, 김건희 ‘명태균 여론조사’ 선고 돌연 연기</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/422/0000887871</t>
+          <t>https://n.news.naver.com/article/025/0003539804</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] “100% 투표” vs “아프다”…김민석·정청래의 ‘깜깜이 당심’ 공략...</t>
+          <t>[더팩트] 오세훈 사법리스크·한동훈 복당 난항…보수 재편 '올스톱'</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/025/0003539514</t>
+          <t>https://n.news.naver.com/article/629/0000518611</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[조선일보] 오세훈 ‘여론조사 대납’ 1심서 시장직 상실형</t>
+          <t>[세계일보] 유시민 “이재명, 지지 기반 무너뜨리고 진영 혼돈 빠뜨릴 수도”</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/023/0003989127</t>
+          <t>https://n.news.naver.com/article/022/0004145449</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[조선일보] 오세훈 "1심 판결 중대한 오류…상급심서 바로잡힐 것"</t>
+          <t>[YTN] 오세훈, 1심 벌금 천만 원에 즉각 항소..."충실히 다툴 것"</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/053/0000060134</t>
+          <t>https://n.news.naver.com/article/052/0002383738</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[SBS] '여론조사 대납' 오세훈 1심 '시장직 상실형' 선고</t>
+          <t>[노컷뉴스] [단독]서울중앙지검 범정 축소…檢 '셀프 힘빼기' 나섰나</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/055/0001374645</t>
+          <t>https://n.news.naver.com/article/079/0004171578</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[MBC] 오세훈 벌금 '1천만 원'‥서울시장직 '상실형'</t>
+          <t>[KBS] [단독] ‘아동 성범죄 혐의’ 최영중…임기 16일치 월급 받아가</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/214/0001513316</t>
+          <t>https://n.news.naver.com/article/056/0012224178</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[KBS] “나경원에 패하자 명태균 찾았다”…오세훈 주장 모두 배척</t>
+          <t>[아시아경제] 이동욱 "액션연기도 감정 교류…새로운 인물 탐험하고 싶죠"</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/056/0012223316</t>
+          <t>https://n.news.naver.com/article/277/0005793956</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[KBS] 오세훈 1심 벌금 1천만 원…“명태균 여론조사 대납 인정”</t>
+          <t>[KBS] ‘36주 낙태’ 산모 살인죄 무죄, 왜?…‘임신 중지 자기결정권’ 손든...</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/056/0012223315</t>
+          <t>https://n.news.naver.com/article/056/0012224214</t>
         </is>
       </c>
     </row>
@@ -579,60 +579,60 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 유시민 “어물전 썩은 내” 김민석 “헛예언은 필패”</t>
+          <t>[서울신문] 정점에서 위기 맞은 오세훈… “정치 재판” 힘 싣는 국힘</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/081/0003663741</t>
+          <t>https://n.news.naver.com/article/081/0003664152</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 송영길 “신천지, 내게도 접근” 정청래 “전대 개입 근거 밝혀라”</t>
+          <t>[노컷뉴스] 與 당권 김민석·정청래·송영길 3파전…최고위원 '친명 5 대 친청 3'</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/020/0003735899</t>
+          <t>https://n.news.naver.com/article/079/0004171586</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>[한국일보] 정청래 "10년 만에 가장 분노"... 연일 '신천지 설' 띄우는 김민석에 경...</t>
+          <t>[서울신문] 김민석·정청래·송영길 3파전 확정… 최고위원 ‘5 대 3’ 명청 대전</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/469/0000943817</t>
+          <t>https://n.news.naver.com/article/081/0003664150</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>[한국일보] "여당 무죄·야당 유죄" 오세훈 선고에 당혹스러운 야권... 보수 '구심점...</t>
+          <t>[동아일보] “차기 대선-총선 구도 흔들려” 오세훈 1심 유죄에 국힘 술렁</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/469/0000943822</t>
+          <t>https://n.news.naver.com/article/020/0003736171</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>[JIBS] 국힘 '李 근저당' 공세.. 민주 "장동혁 6채는?" 역공</t>
+          <t>[한국일보] '정청래 1위' 민심일까, 착시일까... 당 대표 여론조사 두고 명·청 신경...</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/661/0000080369</t>
+          <t>https://n.news.naver.com/article/469/0000944079</t>
         </is>
       </c>
     </row>
@@ -646,60 +646,60 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스TV] "오세훈, 여론조사 의뢰할 동기 있어"…명태균 진술 인정</t>
+          <t>[한겨레] 국힘, 오세훈 1심 뒤 ‘차기 구도’ 촉각…겉으론 “정치재판” 공세</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/422/0000887873</t>
+          <t>https://n.news.naver.com/article/028/0002815549</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>[노컷뉴스] 윤석열·오세훈 유죄…'명태균 게이트' 법원 판단 공통점</t>
+          <t>[동아일보] 국힘 상임위 배분 놓고… 정점식 “멱살까지 잡나” 권영진 “열번도 잡...</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/079/0004171092</t>
+          <t>https://n.news.naver.com/article/020/0003736189</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>[노컷뉴스] "올 것이 왔다"…오세훈 1심 당선무효형에 국힘 '술렁'</t>
+          <t>[한국일보] 거듭된 윤리위 '파행'에 TK는 '외면'...스텝 꼬이는 장동혁</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/079/0004171089</t>
+          <t>https://n.news.naver.com/article/469/0000944074</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] “장동혁 단순 비판, 징계 대상 아냐”… 국힘 윤리위 ‘정적 견제’ 논...</t>
+          <t>[디지털타임스] 확성기 들고 거리에 선 장동혁 “합수본 못 믿어…함성 멈추지 말아야”</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/081/0003663738</t>
+          <t>https://n.news.naver.com/article/029/0003038650</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] ‘여론조사비 대납’ 1심, 오세훈 벌금 1000만원</t>
+          <t>[중앙일보] 겉으론 “정치판결” 비난하지만…‘오세훈 1심’ 복잡한 국힘</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/081/0003663730</t>
+          <t>https://n.news.naver.com/article/025/0003539802</t>
         </is>
       </c>
     </row>
@@ -713,60 +713,60 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] 'G3·야간경제' 시험대 오른 오세훈…15년 전엔 사퇴 뒤 사업 제동</t>
+          <t>[뉴시스] [속보]美재무부, 한국 '환율 관찰대상국' 지정 유지</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/421/0009073865</t>
+          <t>https://n.news.naver.com/article/003/0014085213</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>[한국일보] 오세훈 '사법 리스크', 서울 재개발도 흔들까... '재건축·야간경제' 등...</t>
+          <t>[연합뉴스TV] [속보] 미 재무부, 한국 '환율 관찰대상국' 지위 유지</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/469/0000943823</t>
+          <t>https://n.news.naver.com/article/422/0000888297</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>[경향신문] [단독]“미프진 구해요” 댓글에 달린 ‘이곳’…법 사라진 곳에 쏟아진...</t>
+          <t>[서울신문] [단독] 레버리지 광풍 땐 ‘냉각 시간’ 늘린다</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/032/0003459838</t>
+          <t>https://n.news.naver.com/article/081/0003664145</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>[한겨레] [단독] ‘인천공항 최장 구금’ 피해자 난민신청 6년 만에 ‘체류 허가...</t>
+          <t>[중앙일보] [단독] “침 안놔요, 레이저 쏩니다”…미용시장 침공한 한의원</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/028/0002815341</t>
+          <t>https://n.news.naver.com/article/025/0003539826</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] 4대 금융, 실적 시즌 개막…'가계대출 빗장'에도 11조 순익 전망</t>
+          <t>[중앙일보] [단독] “밝히는 순간, 신뢰 깨져”…요즘 변호사 숨기고픈 ‘비밀’</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/003/0014082510</t>
+          <t>https://n.news.naver.com/article/025/0003539833</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00999999"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -71,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -80,6 +85,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -476,96 +482,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] '튜더 왕조의 설계자' 토머스 크롬웰 처형 [김정한의 역사&amp;오늘]</t>
+          <t>[더팩트] 내분 '외부'로 돌리는 장동혁…'당원 권한 강화' 돌파구 될까</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/421/0009082113</t>
+          <t>https://n.news.naver.com/article/629/0000519461</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] [유효상 칼럼] 왜 국민연금은 '고래의 딜레마(The Whale's Dilemma)'에 빠졌...</t>
+          <t>[뉴스1] 李 대통령이 띄운 임신중지약…하반기 복지위 '뜨거운 감자'</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/008/0005391781</t>
+          <t>https://n.news.naver.com/article/421/0009082119</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[세계일보] 성남시장 “정부 부동산 정책은 ‘규제 일변도’”</t>
+          <t>[서울신문] 민주 “혈세 397억 반드시 회수”… 국힘 “434억 걸린 李 재판 재개”</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/022/0004146385</t>
+          <t>https://n.news.naver.com/article/081/0003665127</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[데일리안] 베를린 퀴어축제 테러 충격…독일 극우당 '반사이익’</t>
+          <t>[동아일보] 경남 진주 ‘발전공기업 통합 본사’ 유치전 참전</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/119/0003115471</t>
+          <t>https://n.news.naver.com/article/020/0003736917</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] "자유는 공짜 아냐" 6·25 정전 73주년에 美 추모행렬</t>
+          <t>[한국일보] 與 '필리버스터·패스트트랙' 개정 착수… "다수당 독주, 헌법 정신 훼손...</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/003/0014091642</t>
+          <t>https://n.news.naver.com/article/469/0000944718</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[서울경제] 트럼프 “美, 금리 내리면 12% 성장 가능...워시는 훌륭한데 이사들이 정...</t>
+          <t>[동아일보] 충남 여야의원 “발전통합본사 유치” 촉구</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/011/0004645793</t>
+          <t>https://n.news.naver.com/article/020/0003736895</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] [세종로의 아침] ‘바퀴벌레’의 힘</t>
+          <t>[YTN] "이번 주 처리" 속도전에 국힘 격앙...또 필버 정국?</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/081/0003665199</t>
+          <t>https://n.news.naver.com/article/052/0002385357</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] ‘IS 추종’ 독일 테러 용의자 사살… “극단주의 경계”</t>
+          <t>[SBS] "새 술은 새 부대에" 또 사의…청와대는 "사실 아냐"</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/081/0003665141</t>
+          <t>https://n.news.naver.com/article/055/0001375816</t>
         </is>
       </c>
     </row>
@@ -577,196 +583,90 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>[조선일보] 패싸움 양상으로 가는 ‘팀 김민석’ vs ‘팀 정청래’</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/023/0003989959</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>[더팩트] '일반 선거인의 인상' 윤석열 유죄 결정적…이재명 판결도 관통</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/629/0000519455</t>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>(해당 시간대 기사 없음)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>[더팩트] 내분 '외부'로 돌리는 장동혁…'당원 권한 강화' 돌파구 될까</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/629/0000519461</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>3) 국민의힘 동정</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>[중앙일보] 정청래 “조국혁신당과 통합했어야…합당했다면 서울시장 이겼을 것”</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/025/0003540488</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>[뉴시스] 정청래 "조국혁신당과 합당했다면 서울시장 이겼을 것"</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/003/0014091416</t>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>(해당 시간대 기사 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>4) 경제 동정</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>3) 국민의힘 동정</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>[뉴시스] "믿을 건 실적 뿐"…역대급 성적표로 반등 모멘텀 잡을까</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/article/003/0014091671</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] ‘장외 정치’ 이어 ‘선거소청 정치’ 나선 장동혁</t>
+          <t>[데일리안] AI 투자 늘린 빅테크, 주가는 급락…"시장이 장기 가치를 과소평가"</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/020/0003736939</t>
+          <t>https://n.news.naver.com/article/119/0003115472</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] [사진] 국힘 시한폭탄 권영진, 정점식에 ‘멱살’ 사과</t>
+          <t>[서울경제] 사우디 핵협상 뒤엔 트럼프 가족?…NYT “트럼프, 원전에 이해충돌 논란...</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/025/0003540553</t>
+          <t>https://n.news.naver.com/article/011/0004645802</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] 李 대통령이 띄운 임신중지약…하반기 복지위 '뜨거운 감자'</t>
+          <t>[뉴스1] 엔비디아 5% 급락…'순환금융' 우려에 SK하닉 ADR 7% 넘게 후퇴</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/421/0009082119</t>
+          <t>https://n.news.naver.com/article/421/0009082077</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] [단독] 빚 연체기록 전부 지워줬더니…6명 중 1명 올해 또 연체했다</t>
+          <t>[서울신문] 한화오션 2분기 영업익 7361억… 98% 뛰어 분기 ‘최대 실적’</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/025/0003540584</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>[이데일리] 괴롭힘 신고해도 64%는 '주의'로 끝…피해자만 웁니다</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/018/0006337863</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>4) 경제 동정</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>[한겨레] [단독] “6살 소녀 파괴한 SNS ‘설계된 중독’ 입증…메타·구글에 승소...</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/028/0002816003</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>[동아일보] [단독]“두더지 심기보다 사람 빼가기… 1명 가면 기업비밀 다 따라가”</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/020/0003736966</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>[동아일보] [단독]배터리 인재를 건설사에 고용, ‘커리어 세탁’ 뒤 기술 빼가</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/020/0003736970</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>[이데일리] [속보]李대통령 “브라질과 방산·항공우주·핵심 광물·디지털경제미래...</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/018/0006337832</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>[MBC] 소비자 심리 3개월 연속 개선‥"반도체 수출 호조·임금 상승 기대"</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/214/0001514242</t>
+          <t>https://n.news.naver.com/article/081/0003665183</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -482,96 +482,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[더팩트] 내분 '외부'로 돌리는 장동혁…'당원 권한 강화' 돌파구 될까</t>
+          <t>[중앙일보] 김부선 “주저없이 ‘알정찍’”∙∙∙정청래 공개 지지 나섰다</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/629/0000519461</t>
+          <t>https://www.joongang.co.kr/article/25448760?utm_source=navernewsstand&amp;utm_medium=referral&amp;utm_campaign=leftbottom4_newsstand&amp;utm_content=260728</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] 李 대통령이 띄운 임신중지약…하반기 복지위 '뜨거운 감자'</t>
+          <t>[동아일보] 장동혁 “부동산 지옥에 사는 국민, 이 정권 지옥으로 보낼 것”</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/421/0009082119</t>
+          <t>https://www.donga.com/news/NewsStand/article/all/20260728/134379395/1?utm_source=newsstand&amp;utm_medium=referral&amp;utm_campaign=main3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 민주 “혈세 397억 반드시 회수”… 국힘 “434억 걸린 李 재판 재개”</t>
+          <t>[한겨레] 장동혁 “임기 연장 개헌 시도 땐 남은 임기 못 채울 것”</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/081/0003665127</t>
+          <t>https://www.hani.co.kr/arti/politics/politics_general/1270320.html?utm_source=naver&amp;utm_medium=referral&amp;utm_campaign=newsstand&amp;utm_term=t2&amp;utm_content=20260728</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 경남 진주 ‘발전공기업 통합 본사’ 유치전 참전</t>
+          <t>[국민일보] 정점식 “권영진 선처 바라” 했지만…”책임 물어야” 쪼개진 국힘</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/020/0003736917</t>
+          <t>https://www.kmib.co.kr/article/view.asp?arcid=9000000103&amp;code=61111111&amp;sid1=pol&amp;cp=nv2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[한국일보] 與 '필리버스터·패스트트랙' 개정 착수… "다수당 독주, 헌법 정신 훼손...</t>
+          <t>[국민일보] 한동훈, ‘보완수사 폐지’ 반대 필리버스터 검토…국힘 공조 이뤄질까</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/469/0000944718</t>
+          <t>https://www.kmib.co.kr/article/view.asp?arcid=9000000107&amp;code=61111111&amp;sid1=pol&amp;cp=nv2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 충남 여야의원 “발전통합본사 유치” 촉구</t>
+          <t>[서울신문] 홍준표 “윤석열·한동훈 데려와 보수 망친 자들, 이제 책임져라”</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/020/0003736895</t>
+          <t>https://www.seoul.co.kr/news/politics/2026/07/28/20260728500197?wlog_sub=svt_006</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[YTN] "이번 주 처리" 속도전에 국힘 격앙...또 필버 정국?</t>
+          <t>[서울신문] 정청래, 충청권 투표 첫날 세종行…“이해찬 정신 계승할 것”</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/052/0002385357</t>
+          <t>https://www.seoul.co.kr/news/politics/2026/07/28/20260728500123?wlog_sub=svt_006</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[SBS] "새 술은 새 부대에" 또 사의…청와대는 "사실 아냐"</t>
+          <t>[MBC] 김민석 "근거 없이 대통령 비난하면, 짚을 건 짚겠다"</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/055/0001375816</t>
+          <t>https://imnews.imbc.com/news/2026/politics/article/6840617_36911.html</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -482,96 +482,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] 김부선 “주저없이 ‘알정찍’”∙∙∙정청래 공개 지지 나섰다</t>
+          <t>[동아일보] 조정식 “현직 대통령 연임, 국민 선택 문제…내년이 개헌 적기”</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://www.joongang.co.kr/article/25448760?utm_source=navernewsstand&amp;utm_medium=referral&amp;utm_campaign=leftbottom4_newsstand&amp;utm_content=260728</t>
+          <t>https://www.donga.com/news/NewsStand/article/all/20260728/134378282/1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 장동혁 “부동산 지옥에 사는 국민, 이 정권 지옥으로 보낼 것”</t>
+          <t>[서울신문] 통영시장 선거 재검표 ‘표차 44→38표’…강석주 당선 유지</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://www.donga.com/news/NewsStand/article/all/20260728/134379395/1?utm_source=newsstand&amp;utm_medium=referral&amp;utm_campaign=main3</t>
+          <t>https://www.seoul.co.kr/news/politics/2026/07/28/20260728500009</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[한겨레] 장동혁 “임기 연장 개헌 시도 땐 남은 임기 못 채울 것”</t>
+          <t>[서울신문] 경찰, 아동 성매매 혐의 최영중 전 청주시의원 구속영장</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://www.hani.co.kr/arti/politics/politics_general/1270320.html?utm_source=naver&amp;utm_medium=referral&amp;utm_campaign=newsstand&amp;utm_term=t2&amp;utm_content=20260728</t>
+          <t>https://www.seoul.co.kr/news/society/2026/07/28/20260728500157</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[국민일보] 정점식 “권영진 선처 바라” 했지만…”책임 물어야” 쪼개진 국힘</t>
+          <t>[동아일보] 與 전대 첫날 온라인 투표 먹통…“충북 권리당원 참여 차질”</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://www.kmib.co.kr/article/view.asp?arcid=9000000103&amp;code=61111111&amp;sid1=pol&amp;cp=nv2</t>
+          <t>https://www.donga.com/news/NewsStand/article/all/20260728/134377773/2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[국민일보] 한동훈, ‘보완수사 폐지’ 반대 필리버스터 검토…국힘 공조 이뤄질까</t>
+          <t>[국민일보] [단독] “檢, 수사 못하는데 파견검사는 가능한가” 선관위 특검 난맥상</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://www.kmib.co.kr/article/view.asp?arcid=9000000107&amp;code=61111111&amp;sid1=pol&amp;cp=nv2</t>
+          <t>https://www.kmib.co.kr/article/view.asp?arcid=0030172407&amp;code=61111111&amp;sid1=pol</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 홍준표 “윤석열·한동훈 데려와 보수 망친 자들, 이제 책임져라”</t>
+          <t>[문화일보] 4개월 전 ‘신천지, 민주당도 가입’ 진술 확보했지만…밍기적 합수본</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://www.seoul.co.kr/news/politics/2026/07/28/20260728500197?wlog_sub=svt_006</t>
+          <t>https://www.munhwa.com/article/11605394</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 정청래, 충청권 투표 첫날 세종行…“이해찬 정신 계승할 것”</t>
+          <t>[머니투데이] "영원한 우정" 李대통령, 룰라 만나고 상파울루行…양국 기업인 '총출동'</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://www.seoul.co.kr/news/politics/2026/07/28/20260728500123?wlog_sub=svt_006</t>
+          <t>https://www.mt.co.kr/politics/2026/07/28/2026072813283328554?STAND=MT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[MBC] 김민석 "근거 없이 대통령 비난하면, 짚을 건 짚겠다"</t>
+          <t>[경향신문] 사설 윤석열 선거법 징역형, 대선 후보의 거짓말 엄중 단죄 마땅하다</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://imnews.imbc.com/news/2026/politics/article/6840617_36911.html</t>
+          <t>https://www.khan.co.kr/article/202607271810001/?nv=stand</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -506,72 +506,72 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 경찰, 아동 성매매 혐의 최영중 전 청주시의원 구속영장</t>
+          <t>[동아일보] 與 전대 첫날 온라인 투표 먹통…“충북 권리당원 참여 차질”</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://www.seoul.co.kr/news/society/2026/07/28/20260728500157</t>
+          <t>https://www.donga.com/news/NewsStand/article/all/20260728/134377773/2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 與 전대 첫날 온라인 투표 먹통…“충북 권리당원 참여 차질”</t>
+          <t>[국민일보] [단독] “檢, 수사 못하는데 파견검사는 가능한가” 선관위 특검 난맥상</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://www.donga.com/news/NewsStand/article/all/20260728/134377773/2</t>
+          <t>https://www.kmib.co.kr/article/view.asp?arcid=0030172407&amp;code=61111111&amp;sid1=pol</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[국민일보] [단독] “檢, 수사 못하는데 파견검사는 가능한가” 선관위 특검 난맥상</t>
+          <t>[문화일보] 4개월 전 ‘신천지, 민주당도 가입’ 진술 확보했지만…밍기적 합수본</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://www.kmib.co.kr/article/view.asp?arcid=0030172407&amp;code=61111111&amp;sid1=pol</t>
+          <t>https://www.munhwa.com/article/11605394</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[문화일보] 4개월 전 ‘신천지, 민주당도 가입’ 진술 확보했지만…밍기적 합수본</t>
+          <t>[머니투데이] "영원한 우정" 李대통령, 룰라 만나고 상파울루行…양국 기업인 '총출동'</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://www.munhwa.com/article/11605394</t>
+          <t>https://www.mt.co.kr/politics/2026/07/28/2026072813283328554?STAND=MT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] "영원한 우정" 李대통령, 룰라 만나고 상파울루行…양국 기업인 '총출동'</t>
+          <t>[문화일보] “국회로 돌아가겠다, 당장”… 정성호, 이미 세달 전 사의 표명했다</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://www.mt.co.kr/politics/2026/07/28/2026072813283328554?STAND=MT</t>
+          <t>https://www.munhwa.com/article/11605444</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[경향신문] 사설 윤석열 선거법 징역형, 대선 후보의 거짓말 엄중 단죄 마땅하다</t>
+          <t>[중앙일보] 김부선 “주저없이 ‘알정찍’”∙∙∙정청래 공개 지지 나섰다</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://www.khan.co.kr/article/202607271810001/?nv=stand</t>
+          <t>https://www.joongang.co.kr/article/25448760</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -518,24 +518,24 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[국민일보] [단독] “檢, 수사 못하는데 파견검사는 가능한가” 선관위 특검 난맥상</t>
+          <t>[문화일보] 4개월 전 ‘신천지, 민주당도 가입’ 진술 확보했지만…밍기적 합수본</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://www.kmib.co.kr/article/view.asp?arcid=0030172407&amp;code=61111111&amp;sid1=pol</t>
+          <t>https://www.munhwa.com/article/11605394</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[문화일보] 4개월 전 ‘신천지, 민주당도 가입’ 진술 확보했지만…밍기적 합수본</t>
+          <t>[국민일보] [단독] “檢, 수사 못하는데 파견검사는 가능한가” 선관위 특검 난맥상</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://www.munhwa.com/article/11605394</t>
+          <t>https://www.kmib.co.kr/article/view.asp?arcid=0030172407&amp;code=61111111&amp;sid1=pol</t>
         </is>
       </c>
     </row>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -455,14 +455,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>일일 정치 주요뉴스 8/21(금)</t>
+          <t>일일 정치 주요뉴스 8/22(토)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>(기준: 2026-08-20 22:00 ~ 2026-08-21 06:00)</t>
+          <t>(기준: 2026-08-21 22:00 ~ 2026-08-22 06:00)</t>
         </is>
       </c>
     </row>
@@ -476,96 +476,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] 오세훈-김윤덕 용산공원 두고 “평행선” icon_video</t>
+          <t>[서울신문] 靑 “조희대, 헌정사 초유 일방통보… 대통령 임명권 존중 없어”</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://www.joongang.co.kr/article/25454760</t>
+          <t>https://www.seoul.co.kr/news/politics/2026/08/21/20260821500235</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[이데일리] 김여정, UFS 축소에 "韓, 美 상전 둔 허수아비"…李대통령도 원색 비난</t>
+          <t>[이데일리] “한동훈은 응답하라”…노웅래 2심 무죄에 ‘돈봉투 부스럭’ 소환</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://www.edaily.co.kr/news/contents/NewsStand/vbs_real/brg.asp?bCode=B03ns&amp;sgb=E&amp;newsid=06248406645549288</t>
+          <t>https://www.edaily.co.kr/news/read?newsId=04782246645549616</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 국힘, 현역의원 4인 당원권 정지… 총선 출마 길 막았다</t>
+          <t>[서울신문] 李대통령, ‘집중호우 피해’ 거제·통영 특별재난지역 선포</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://www.seoul.co.kr/news/politics/2026/08/21/20260821001005</t>
+          <t>https://www.seoul.co.kr/news/politics/2026/08/21/20260821500319</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 홍장원-조성현 등 무혐의 뒤집은 종합특검… 공은 법원으로</t>
+          <t>[한겨레] ‘시장직 걸린’ 오세훈 항소심 시작…명태균 관련 등 혐의 부인</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://www.donga.com/news/NewsStand/article/all/20260821/134516262/2</t>
+          <t>https://www.hani.co.kr/arti/society/society_general/1274051.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 靑, ‘조희대의 대법관 서면 제청’에 “유례없는 일방 통보”</t>
+          <t>[노컷뉴스] 3 "李 대통령과 통화했다고 한 적 없다" 김관영 전 지사 조사 마쳐</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://www.donga.com/news/NewsStand/article/all/20260821/134516526/2</t>
+          <t>https://www.nocutnews.co.kr/news/6566311</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 김민석, 지명직 최고 지명… 친청계 “당헌 위반” 반발</t>
+          <t>[국민일보] 초등학생에 “오빠 해봐요”…정청래·하정우 아동학대 무혐의 종결</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://www.seoul.co.kr/news/politics/2026/08/21/20260821005004</t>
+          <t>https://www.kmib.co.kr/article/view.asp?arcid=9000005001&amp;code=61111511&amp;sid1=pol</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[이데일리] 北, 평양서 탄도미사일 10여발 '무더기 발사'</t>
+          <t>[동아일보] 국힘 의총서 장동혁 추진 ‘당협위원장 물갈이’ 제동</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://www.edaily.co.kr/news/contents/NewsStand/vbs_real/brg.asp?bCode=B09ns&amp;sgb=E&amp;newsid=05251286645549288</t>
+          <t>https://www.donga.com/news/NewsStand/article/all/20260821/134522956/2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[세계일보] 李대통령, 최태원과 만찬 회동… '3대 메가' 대미투자 논의 주목</t>
+          <t>[동아일보] 김민석 ‘지명직 최고’ 임명에 반발… 친청계 3명 퇴장</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://www.segye.com/newsView/20260820524975</t>
+          <t>https://www.donga.com/news/NewsStand/article/all/20260821/134522954/2</t>
         </is>
       </c>
     </row>
@@ -579,60 +579,60 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>[경향신문] [단독]‘오빠 강요 논란’ 정청래·하정우, 아동학대 ‘무혐의’ 종결</t>
+          <t>[중앙일보] 김민석과 대립→중립→비판...김어준 아슬아슬 ‘완급조절’ 왜</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/032/0003465524</t>
+          <t>https://n.news.naver.com/article/025/0003546003</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>[데일리안] 김민석 '민심 창구' 될까, '명심 창구' 될까…시험대 오른 당정청 관계</t>
+          <t>[뉴스1] '새벽 TV'부터 조직 문화까지…김민석, 민주당 '싹' 바꾼다</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/119/0003123695</t>
+          <t>https://n.news.naver.com/article/421/0009126747</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>[세계일보] 김민석의 “민주당 TV”에 ‘배은망덕’ 비난…“뉴스공장 이기겠나”...</t>
+          <t>[YTN] 김민석 "이진숙 징계 요청한 국힘 당원께 감사...제명 반드시 이뤄낼 것...</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/022/0004152504</t>
+          <t>https://n.news.naver.com/article/052/0002396615</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] ‘여섯 어른’ 순례 마친 김민석… 與전대 갈등 딛고 통합 시동</t>
+          <t>[동아일보] 김민석 ‘지명직 최고’ 임명에 반발… 친청계 3명은 의결도 안하고 퇴...</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/081/0003672146</t>
+          <t>https://n.news.naver.com/article/020/0003742564</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 김민석 “민주당 30년 연속 집권 틀 짜겠다”</t>
+          <t>[중앙일보] 김민석 제1파트너는 강훈식…‘우군’ 송영길도 역할 커질 듯</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/020/0003742370</t>
+          <t>https://n.news.naver.com/article/353/0000056438</t>
         </is>
       </c>
     </row>
@@ -646,60 +646,60 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스] '명태균 의혹' 尹·오세훈 오늘 나란히 2심 첫 공판</t>
+          <t>[뉴시스] 국힘, 비당권파 중징계에 내홍 격화…"장동혁은 찌질이 보수" "윤리위의...</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/001/0016262651</t>
+          <t>https://n.news.naver.com/article/003/0014141464</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] 장동혁-정점식, 국힘 '투톱' 미묘한 입장차…정점식 역할론 주목</t>
+          <t>[노컷뉴스] '비장횡사', '당협 물갈이'…장동혁 당권 연장 포석?</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/003/0014139475</t>
+          <t>https://n.news.naver.com/article/079/0004181151</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>[문화일보] ‘조희대 씨’로 부른 김민석에 “김민석씨, 정신차리세요”…한동훈의...</t>
+          <t>[YTN] 정점식 "대통령의 '대북 스토킹'...민주당식 굴종은 사기극"</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/021/0002812718</t>
+          <t>https://n.news.naver.com/article/052/0002396626</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>[더팩트] '명태균 여론조사' 윤석열·오세훈 나란히 2라운드 돌입</t>
+          <t>[YTN] 정점식, 암참 회장 접견..."한미통상 다루는 정부 방식 아쉬워"</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/629/0000526241</t>
+          <t>https://n.news.naver.com/article/052/0002396611</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] 한동훈, 4명 중징계에 “자의적 징계 정치…국민께 버림받을 것”</t>
+          <t>[YTN] 정점식, 청년 지방의원 만나 "총선 위해 '중·수·청' 마음 사야"</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/025/0003545749</t>
+          <t>https://n.news.naver.com/article/052/0002396598</t>
         </is>
       </c>
     </row>
@@ -713,60 +713,60 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] ‘용산 공원’ 접점 못찾은 김윤덕-오세훈… 주변 개발 - 용적률 완화 내...</t>
+          <t>[조선일보] [박정훈 칼럼] ‘어제의 이재명’과 싸우는 오늘의 추미애</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/020/0003742309</t>
+          <t>https://n.news.naver.com/article/023/0003994241</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] “이재명 불안초조” 조롱…한국 빼고 트럼프·김정은 ‘핵 직거래’? ...</t>
+          <t>[중앙일보] “기술은 수명 3년뿐? 엔비디아는 다르다”…월가의 위험한 베팅</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/081/0003672131</t>
+          <t>https://n.news.naver.com/article/025/0003545995</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] [단독]따릉이 462만명 유출 겪은 서울시…'해킹 미신고' 징계</t>
+          <t>[경향신문] 코스피 발목 잡는 ‘보이지 않는 손’, 미국 장기국채 금리의 정체[경제...</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/421/0009124883</t>
+          <t>https://n.news.naver.com/article/032/0003465662</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>[국민일보] [단독] 공급대책에 밀린 ‘국립여성사박물관 건립’ 원점으로</t>
+          <t>[뉴시스] 집 지을 것인가, 공원 지킬 것인가…용산공원 '뜨거운 감자'[주택공급 ...</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/005/0001868094</t>
+          <t>https://n.news.naver.com/article/003/0014141471</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>[서울경제] 이재명 대통령, 최태원 SK 회장과 비공개 만찬…반도체 투자·노사 현안...</t>
+          <t>[중앙일보] “버텨야죠, 폐버스는 아니니까” 고시촌 빨래방서 본 청춘의 좌절</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/011/0004653684</t>
+          <t>https://n.news.naver.com/article/025/0003545998</t>
         </is>
       </c>
     </row>
